--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE146"/>
+  <dimension ref="A1:AE145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 48380-2021</t>
+          <t>A 57997-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44451</v>
+        <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 57997-2021</t>
+          <t>A 64627-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44487</v>
+        <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 64627-2021</t>
+          <t>A 60021-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44511</v>
+        <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60021-2021</t>
+          <t>A 54411-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44494</v>
+        <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54411-2021</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44473</v>
+        <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 53784-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44739</v>
+        <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53784-2021</t>
+          <t>A 52729-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44469</v>
+        <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52729-2021</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44467</v>
+        <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44472</v>
+        <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44845</v>
+        <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45235</v>
+        <v>45029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44868</v>
+        <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2431,13 +2431,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2490,14 +2485,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44939</v>
+        <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2553,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,8 +2577,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>45478</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,13 +2655,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45826</v>
+        <v>45756</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2734,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45602</v>
+        <v>45302</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45314</v>
+        <v>45397</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2879,13 +2874,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45161</v>
+        <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2957,8 +2947,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45701</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3030,13 +3025,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3079,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3093,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45608</v>
+        <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3109,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3152,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3166,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46098</v>
+        <v>44636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3182,7 +3172,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3225,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3239,10 +3229,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45219</v>
+        <v>45602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3254,13 +3244,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3303,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3317,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44746</v>
+        <v>44923</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3333,7 +3318,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3376,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3386,14 +3371,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45981</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3406,7 +3391,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3449,7 +3434,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3463,10 +3448,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46127</v>
+        <v>45544</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3478,13 +3463,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3527,7 +3507,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3541,10 +3521,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45078</v>
+        <v>45608</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3557,7 +3537,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3600,7 +3580,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3614,10 +3594,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45583</v>
+        <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3630,7 +3610,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3673,7 +3653,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3687,10 +3667,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45751</v>
+        <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3703,7 +3683,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3746,7 +3726,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3756,14 +3736,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45751</v>
+        <v>44939</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3776,7 +3756,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3819,7 +3799,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3836,7 +3816,7 @@
         <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3854,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3897,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3911,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45930</v>
+        <v>45259</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3926,8 +3906,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3970,7 +3955,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3984,10 +3969,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45733</v>
+        <v>45583</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4000,7 +3985,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4028,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4042,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45733</v>
+        <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4116,7 +4101,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4115,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45161</v>
+        <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4146,7 +4131,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4174,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4188,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45356</v>
+        <v>46098</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4219,7 +4204,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4247,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4261,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46034</v>
+        <v>45107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4292,7 +4277,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4320,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,10 +4334,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45062</v>
+        <v>45259</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4364,8 +4349,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4408,7 +4398,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,10 +4412,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46043</v>
+        <v>46127</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4437,8 +4427,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4481,7 +4476,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4495,10 +4490,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45565</v>
+        <v>44945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4511,7 +4506,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4554,7 +4549,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4564,14 +4559,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45817</v>
+        <v>45981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4584,7 +4579,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4627,7 +4622,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4641,10 +4636,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44992</v>
+        <v>44882</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4657,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>45565</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4735,7 +4730,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45702</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4807,8 +4802,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44981</v>
+        <v>44882</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4880,8 +4880,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45702</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4953,13 +4958,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45702</v>
+        <v>45356</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5031,13 +5031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5080,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5094,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45145</v>
+        <v>45817</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5110,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5153,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5167,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45161</v>
+        <v>45930</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5178,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5221,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5236,14 +5231,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45003</v>
+        <v>45078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5251,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5294,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5308,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46149</v>
+        <v>45701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5328,8 +5323,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>16.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45478</v>
+        <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45219</v>
+        <v>46149</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5474,13 +5474,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.2</v>
+        <v>16.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5523,7 +5518,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5537,10 +5532,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45219</v>
+        <v>44524</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5552,13 +5547,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5591,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45219</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,13 +5620,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5696,7 +5681,7 @@
         <v>46167</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5752,7 +5737,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5766,10 +5751,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45107</v>
+        <v>44875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5781,8 +5766,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5815,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5835,14 +5825,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45394</v>
+        <v>46178</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5854,8 +5844,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5915,7 +5910,7 @@
         <v>46177</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5976,7 +5971,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5990,10 +5985,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6005,13 +6000,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6044,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6068,10 +6058,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44882</v>
+        <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6081,11 +6071,6 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6132,7 +6117,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6146,10 +6131,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44746</v>
+        <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,8 +6146,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6205,7 +6195,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45163</v>
+        <v>46246</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6234,8 +6224,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6278,7 +6273,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6292,10 +6287,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44923</v>
+        <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6308,7 +6303,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6351,7 +6346,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6365,10 +6360,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44923</v>
+        <v>46260</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6381,7 +6376,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6424,7 +6419,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6438,10 +6433,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46189</v>
+        <v>45702</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6453,8 +6448,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6497,7 +6497,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45106</v>
+        <v>46268</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45259</v>
+        <v>44981</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6604,13 +6604,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6653,7 +6648,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6663,14 +6658,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45370</v>
+        <v>44592</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6682,13 +6677,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6731,7 +6721,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6745,10 +6735,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44882</v>
+        <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6760,13 +6750,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6809,7 +6794,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6823,10 +6808,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45565</v>
+        <v>45161</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6839,7 +6824,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6867,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6892,14 +6877,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44592</v>
+        <v>45356</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6912,7 +6897,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6955,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6965,14 +6950,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45302</v>
+        <v>45003</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6985,7 +6970,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7028,7 +7013,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7042,10 +7027,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44992</v>
+        <v>45062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7057,13 +7042,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46246</v>
+        <v>45145</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7135,13 +7115,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7184,7 +7159,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7198,10 +7173,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46247</v>
+        <v>45302</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7214,7 +7189,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>9.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7257,7 +7232,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7271,10 +7246,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45259</v>
+        <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7292,7 +7267,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7310,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7324,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45397</v>
+        <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7364,8 +7339,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7408,7 +7388,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7422,10 +7402,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46260</v>
+        <v>45161</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7438,7 +7418,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7481,7 +7461,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7495,10 +7475,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45702</v>
+        <v>45235</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7510,13 +7490,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7559,7 +7534,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7573,10 +7548,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44524</v>
+        <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7588,8 +7563,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7632,7 +7612,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7646,10 +7626,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45231</v>
+        <v>45751</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7662,7 +7642,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7705,7 +7685,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7719,10 +7699,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45078</v>
+        <v>44845</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7735,7 +7715,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7778,7 +7758,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7792,10 +7772,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46268</v>
+        <v>45370</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7813,7 +7793,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7856,7 +7836,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7870,10 +7850,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45356</v>
+        <v>44923</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7886,7 +7866,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7929,7 +7909,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7943,10 +7923,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45369</v>
+        <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7959,7 +7939,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7982,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +7996,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45107</v>
+        <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8031,8 +8011,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>10.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8060,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8074,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45373</v>
+        <v>45219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8104,8 +8089,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45702</v>
+        <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8177,13 +8167,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8211,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8240,10 +8225,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44977</v>
+        <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8255,8 +8240,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8289,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8303,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45544</v>
+        <v>45702</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8328,8 +8318,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45029</v>
+        <v>44746</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8402,7 +8397,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45701</v>
+        <v>44992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8474,8 +8469,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45265</v>
+        <v>45394</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8547,13 +8547,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8605,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45511</v>
+        <v>45265</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8625,8 +8620,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44879</v>
+        <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8698,13 +8698,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8747,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45666</v>
+        <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8774,6 +8769,11 @@
       <c r="G108" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45478</v>
+        <v>45666</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8910,7 +8910,7 @@
         <v>45477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8966,24 +8966,24 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45756</v>
+        <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9039,7 +9039,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44637</v>
+        <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9068,8 +9068,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9112,7 +9117,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9126,10 +9131,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45434</v>
+        <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9141,13 +9146,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44918</v>
+        <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.7</v>
+        <v>44.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9263,7 +9263,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44830</v>
+        <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>44.5</v>
+        <v>17.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44543</v>
+        <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44988</v>
+        <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9492,14 +9492,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45565</v>
+        <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45348</v>
+        <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7</v>
+        <v>15.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44858</v>
+        <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>15.8</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9701,7 +9701,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45608</v>
+        <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9730,8 +9730,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9774,7 +9779,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9788,10 +9793,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45434</v>
+        <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9803,13 +9808,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9866,10 +9866,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44988</v>
+        <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9925,7 +9925,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9939,10 +9939,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45582</v>
+        <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>13.8</v>
+        <v>40.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44936</v>
+        <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>40.1</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45607</v>
+        <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>55.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10144,7 +10144,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44936</v>
+        <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>55.2</v>
+        <v>13.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10217,7 +10217,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45393</v>
+        <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10290,7 +10290,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10304,10 +10304,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45002</v>
+        <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>12.7</v>
+        <v>11.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45608</v>
+        <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>11.6</v>
+        <v>31.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45709</v>
+        <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>31.1</v>
+        <v>15.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45901</v>
+        <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>15.1</v>
+        <v>5.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10582,7 +10582,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46030</v>
+        <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10611,8 +10611,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10655,7 +10660,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10669,10 +10674,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10690,7 +10695,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>20</v>
+        <v>21.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10733,7 +10738,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10750,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10768,7 +10773,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10811,7 +10816,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10828,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10846,7 +10851,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>19.8</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10889,7 +10894,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10906,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10924,7 +10929,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10967,7 +10972,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10981,10 +10986,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10996,13 +11001,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>8.199999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46058</v>
+        <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>27.6</v>
+        <v>8.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11118,7 +11118,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46136</v>
+        <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11147,8 +11147,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11191,7 +11196,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11208,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11226,7 +11231,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>11.1</v>
+        <v>17.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11286,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11304,7 +11309,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>17.7</v>
+        <v>28.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11347,7 +11352,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11364,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11382,7 +11387,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>28.1</v>
+        <v>15.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11425,7 +11430,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S 2015-2026</t>
+          <t>S 2017-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11442,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11460,7 +11465,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11500,10 +11505,10 @@
       </c>
       <c r="V144" s="2" t="inlineStr"/>
     </row>
-    <row r="145" ht="15" customHeight="1">
+    <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S 2017-2026</t>
+          <t>S 2047-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11517,10 +11522,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11538,7 +11543,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11577,84 +11582,6 @@
         <v>0</v>
       </c>
       <c r="V145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>S 2047-2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E146" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I146" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52729-2021</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44467</v>
+        <v>44472</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44472</v>
+        <v>44845</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 52729-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45751</v>
+        <v>44467</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45701</v>
+        <v>45302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44746</v>
+        <v>44882</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,8 +2212,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2261,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45029</v>
+        <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2291,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45078</v>
+        <v>45163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2364,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45231</v>
+        <v>44923</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2475,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45565</v>
+        <v>44923</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2583,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45478</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2653,6 +2658,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2699,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45756</v>
+        <v>45235</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45302</v>
+        <v>44868</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2802,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45397</v>
+        <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45259</v>
+        <v>45602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,13 +2957,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3001,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,8 +3030,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3079,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3093,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46043</v>
+        <v>45370</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3098,8 +3108,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3157,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3152,14 +3167,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44636</v>
+        <v>44939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3172,7 +3187,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3230,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3229,10 +3244,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45602</v>
+        <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3260,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3303,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3317,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44923</v>
+        <v>46127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3317,8 +3332,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3361,7 +3381,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3395,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45608</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3391,7 +3411,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3434,7 +3454,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3448,10 +3468,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45544</v>
+        <v>45259</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3463,8 +3483,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3507,7 +3532,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3521,10 +3546,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45608</v>
+        <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3537,7 +3562,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3580,7 +3605,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3594,10 +3619,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45733</v>
+        <v>45314</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3609,8 +3634,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3653,7 +3683,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3667,10 +3697,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45733</v>
+        <v>45565</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3683,7 +3713,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3726,7 +3756,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3736,14 +3766,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44939</v>
+        <v>45817</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3756,7 +3786,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3799,7 +3829,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3813,10 +3843,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45259</v>
+        <v>44882</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3864,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3907,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3921,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45259</v>
+        <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3906,13 +3936,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3980,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3965,14 +3990,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45583</v>
+        <v>44592</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3985,7 +4010,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4028,7 +4053,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4042,10 +4067,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44868</v>
+        <v>45161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4058,7 +4083,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4101,7 +4126,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4115,10 +4140,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45478</v>
+        <v>45302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4131,7 +4156,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4174,7 +4199,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4184,14 +4209,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46098</v>
+        <v>45981</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4204,7 +4229,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4247,7 +4272,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4261,10 +4286,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45107</v>
+        <v>45701</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4276,8 +4301,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4320,7 +4350,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4334,10 +4364,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45259</v>
+        <v>44992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4355,7 +4385,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4398,7 +4428,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4412,10 +4442,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46127</v>
+        <v>46149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4427,13 +4457,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.1</v>
+        <v>16.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4476,7 +4501,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4490,10 +4515,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44945</v>
+        <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4505,8 +4530,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4549,7 +4579,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4559,14 +4589,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45981</v>
+        <v>44746</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4579,7 +4609,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4622,7 +4652,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4636,10 +4666,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44882</v>
+        <v>46034</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4651,13 +4681,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4700,7 +4725,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4714,10 +4739,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45565</v>
+        <v>46167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4730,7 +4755,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4773,7 +4798,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4787,10 +4812,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45702</v>
+        <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4802,13 +4827,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4871,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4885,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44882</v>
+        <v>45583</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4880,13 +4900,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4944,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4958,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4974,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45356</v>
+        <v>45751</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5047,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5090,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5104,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45817</v>
+        <v>45751</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5105,7 +5120,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5163,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5177,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45930</v>
+        <v>46177</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5177,8 +5192,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5221,7 +5241,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5235,10 +5255,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45078</v>
+        <v>45259</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5250,8 +5270,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5294,7 +5319,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5308,10 +5333,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45701</v>
+        <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5329,7 +5354,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5397,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5411,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>45733</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5402,7 +5427,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5445,7 +5470,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5459,10 +5484,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46149</v>
+        <v>45733</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5475,7 +5500,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5518,7 +5543,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5532,10 +5557,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44524</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5548,7 +5573,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5591,7 +5616,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5605,10 +5630,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45161</v>
+        <v>45356</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5621,7 +5646,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5664,7 +5689,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5678,10 +5703,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46167</v>
+        <v>46189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5694,7 +5719,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5737,7 +5762,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5751,10 +5776,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44875</v>
+        <v>45062</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5766,13 +5791,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5815,7 +5835,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5829,10 +5849,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46178</v>
+        <v>45259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5850,7 +5870,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5913,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5907,10 +5927,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46177</v>
+        <v>45397</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5922,13 +5942,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5971,7 +5986,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5985,10 +6000,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46189</v>
+        <v>44992</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6000,8 +6015,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6044,7 +6064,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6058,10 +6078,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6074,7 +6094,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6117,7 +6137,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6131,10 +6151,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45219</v>
+        <v>44945</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6146,13 +6166,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6195,7 +6210,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6209,10 +6224,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46246</v>
+        <v>44981</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6224,13 +6239,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6273,7 +6283,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6287,10 +6297,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46247</v>
+        <v>45702</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6302,8 +6312,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6346,7 +6361,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6360,10 +6375,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46260</v>
+        <v>44524</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6376,7 +6391,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6419,7 +6434,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6436,7 +6451,7 @@
         <v>45702</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6454,7 +6469,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6497,7 +6512,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6511,10 +6526,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46268</v>
+        <v>45702</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6532,7 +6547,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6575,7 +6590,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6589,10 +6604,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44981</v>
+        <v>45145</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6605,7 +6620,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6648,7 +6663,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6658,14 +6673,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44592</v>
+        <v>45161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6678,7 +6693,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6721,7 +6736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6731,14 +6746,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45369</v>
+        <v>45003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6751,7 +6766,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6794,7 +6809,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6808,10 +6823,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45161</v>
+        <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6823,8 +6838,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6867,7 +6887,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6881,10 +6901,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45356</v>
+        <v>45231</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6897,7 +6917,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6960,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6950,14 +6970,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45003</v>
+        <v>46247</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6970,7 +6990,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7013,7 +7033,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7027,10 +7047,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45062</v>
+        <v>45478</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7043,7 +7063,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45145</v>
+        <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,8 +7135,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7159,7 +7184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7173,10 +7198,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45302</v>
+        <v>45219</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7188,8 +7213,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7232,7 +7262,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7246,10 +7276,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44992</v>
+        <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7261,13 +7291,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7310,7 +7335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7327,7 +7352,7 @@
         <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7345,7 +7370,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7388,7 +7413,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7402,10 +7427,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45161</v>
+        <v>46260</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7418,7 +7443,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7461,7 +7486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7475,10 +7500,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45235</v>
+        <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7491,7 +7516,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7534,7 +7559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7544,14 +7569,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45106</v>
+        <v>45394</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7563,13 +7588,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7612,7 +7632,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7626,10 +7646,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45751</v>
+        <v>45356</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7642,7 +7662,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7685,7 +7705,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7699,10 +7719,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44845</v>
+        <v>45369</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7715,7 +7735,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7758,7 +7778,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7772,10 +7792,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45370</v>
+        <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7787,13 +7807,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7836,7 +7851,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7850,10 +7865,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44923</v>
+        <v>45373</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7866,7 +7881,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7909,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7923,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45107</v>
+        <v>45702</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7938,8 +7953,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7982,7 +8002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7996,10 +8016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45219</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8011,13 +8031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8060,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8074,10 +8089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45219</v>
+        <v>46268</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8095,7 +8110,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8138,7 +8153,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8152,10 +8167,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45163</v>
+        <v>45544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8168,7 +8183,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8211,7 +8226,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8225,10 +8240,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45702</v>
+        <v>45029</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8240,13 +8255,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8289,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8303,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45702</v>
+        <v>45701</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8318,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44746</v>
+        <v>45265</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,8 +8401,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8454,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44992</v>
+        <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8469,13 +8479,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8528,14 +8533,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45394</v>
+        <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8547,8 +8552,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8601,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8605,10 +8615,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45265</v>
+        <v>45666</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8620,13 +8630,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8674,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8688,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45511</v>
+        <v>45478</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8704,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8747,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8761,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44879</v>
+        <v>45477</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,13 +8776,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45666</v>
+        <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45477</v>
+        <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 52729-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44472</v>
+        <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44845</v>
+        <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52729-2021</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44467</v>
+        <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44882</v>
+        <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,13 +2212,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2261,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44746</v>
+        <v>45701</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2291,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45163</v>
+        <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2364,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44923</v>
+        <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2480,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44923</v>
+        <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2553,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45106</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2583,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2660,13 +2655,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45235</v>
+        <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44868</v>
+        <v>45259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2811,8 +2801,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46098</v>
+        <v>44636</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45602</v>
+        <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2958,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44875</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3030,13 +3025,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3079,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3093,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45370</v>
+        <v>45544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3108,13 +3098,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3157,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3167,14 +3152,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44939</v>
+        <v>45602</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3187,7 +3172,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3230,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3244,10 +3229,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44636</v>
+        <v>45826</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3260,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3303,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3317,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46127</v>
+        <v>45733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3332,13 +3317,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3381,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3395,10 +3375,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45608</v>
+        <v>45733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3411,7 +3391,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3454,7 +3434,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3464,14 +3444,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45259</v>
+        <v>44939</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3483,13 +3463,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3532,7 +3507,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3546,10 +3521,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45930</v>
+        <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3562,7 +3537,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3605,7 +3580,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3619,10 +3594,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3640,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3683,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3697,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45565</v>
+        <v>45259</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3712,8 +3687,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3756,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3770,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45817</v>
+        <v>45608</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3786,7 +3766,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3829,7 +3809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3843,10 +3823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44882</v>
+        <v>45583</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3858,13 +3838,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3907,7 +3882,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3921,10 +3896,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45565</v>
+        <v>44868</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3937,7 +3912,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3980,7 +3955,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3990,14 +3965,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44592</v>
+        <v>45478</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4010,7 +3985,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4053,7 +4028,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4067,10 +4042,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45161</v>
+        <v>45107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4083,7 +4058,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4126,7 +4101,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4140,10 +4115,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45302</v>
+        <v>45259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4155,8 +4130,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4199,7 +4179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4209,14 +4189,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45981</v>
+        <v>44945</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4229,7 +4209,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4272,7 +4252,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4286,10 +4266,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45701</v>
+        <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4307,7 +4287,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4350,7 +4330,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4364,10 +4344,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44992</v>
+        <v>45702</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4385,7 +4365,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4428,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4438,14 +4418,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46149</v>
+        <v>45981</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4458,7 +4438,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>16.7</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4501,7 +4481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4515,10 +4495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45219</v>
+        <v>44882</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4536,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4579,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4593,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44746</v>
+        <v>45610</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4609,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4652,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4666,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46034</v>
+        <v>45356</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4682,7 +4662,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4725,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4739,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46167</v>
+        <v>45078</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4755,7 +4735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4798,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4812,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45078</v>
+        <v>45701</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4825,6 +4805,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4871,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4885,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45583</v>
+        <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4901,7 +4886,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4944,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4958,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46043</v>
+        <v>45373</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4974,7 +4959,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5017,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5031,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45751</v>
+        <v>44524</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5047,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5090,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5104,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45751</v>
+        <v>45161</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5120,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5163,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5177,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46177</v>
+        <v>44875</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5198,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5241,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5255,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45259</v>
+        <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5270,13 +5255,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5319,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5333,10 +5313,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46178</v>
+        <v>46127</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5350,11 +5330,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5397,7 +5377,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5411,10 +5391,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45733</v>
+        <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5426,8 +5406,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5470,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5484,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45733</v>
+        <v>45565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5500,7 +5485,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5543,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5557,10 +5542,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45702</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5572,8 +5557,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5616,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5630,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45356</v>
+        <v>45817</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5646,7 +5636,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5689,7 +5679,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5703,10 +5693,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46189</v>
+        <v>45930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5719,7 +5709,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5762,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5776,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45062</v>
+        <v>44981</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5792,7 +5782,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5835,7 +5825,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5845,14 +5835,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45259</v>
+        <v>44592</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5864,13 +5854,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5913,7 +5898,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5927,10 +5912,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45397</v>
+        <v>45369</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5943,7 +5928,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5986,7 +5971,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6000,10 +5985,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44992</v>
+        <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6015,13 +6000,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6064,7 +6044,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6078,10 +6058,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45610</v>
+        <v>45356</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6094,7 +6074,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6137,7 +6117,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6151,10 +6131,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44945</v>
+        <v>46149</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6167,7 +6147,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>16.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6210,7 +6190,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6220,14 +6200,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44981</v>
+        <v>45003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6240,7 +6220,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6283,7 +6263,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6297,10 +6277,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45702</v>
+        <v>45062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6312,13 +6292,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6361,7 +6336,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6375,10 +6350,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44524</v>
+        <v>46167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6391,7 +6366,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6434,7 +6409,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6448,10 +6423,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6463,13 +6438,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6512,7 +6482,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6526,10 +6496,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45702</v>
+        <v>45302</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6541,13 +6511,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6590,7 +6555,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6604,10 +6569,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45145</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6619,8 +6584,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6663,7 +6633,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6677,10 +6647,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45161</v>
+        <v>46178</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6692,8 +6662,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6736,7 +6711,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6746,14 +6721,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45003</v>
+        <v>46177</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6765,8 +6740,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6809,7 +6789,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6823,10 +6803,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46246</v>
+        <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6844,7 +6824,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6887,7 +6867,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6901,10 +6881,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45231</v>
+        <v>46189</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6917,7 +6897,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6960,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6974,10 +6954,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46247</v>
+        <v>45161</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6990,7 +6970,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>9.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7033,7 +7013,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7047,10 +7027,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45478</v>
+        <v>45235</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7063,7 +7043,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45219</v>
+        <v>45106</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7141,7 +7121,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7184,7 +7164,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7198,10 +7178,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45219</v>
+        <v>45751</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7213,13 +7193,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7262,7 +7237,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7276,10 +7251,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45078</v>
+        <v>46246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7291,8 +7266,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7315,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7329,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45219</v>
+        <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7364,13 +7344,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7413,7 +7388,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7427,10 +7402,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46260</v>
+        <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7443,7 +7418,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7486,7 +7461,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7500,10 +7475,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45107</v>
+        <v>45370</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7515,8 +7490,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7559,7 +7539,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7569,14 +7549,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45394</v>
+        <v>44923</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7589,7 +7569,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7632,7 +7612,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7646,10 +7626,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7662,7 +7642,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7705,7 +7685,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7719,10 +7699,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45369</v>
+        <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7734,8 +7714,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7778,7 +7763,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7792,10 +7777,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45107</v>
+        <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7807,8 +7792,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45373</v>
+        <v>45163</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45702</v>
+        <v>46260</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7953,13 +7943,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7987,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +8001,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>46268</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8031,8 +8016,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8065,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8079,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46268</v>
+        <v>45702</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8110,7 +8100,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8153,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8167,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45544</v>
+        <v>45702</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8182,8 +8172,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8240,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45029</v>
+        <v>44746</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8256,7 +8251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45701</v>
+        <v>44992</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8328,8 +8323,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8382,14 +8382,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45265</v>
+        <v>45394</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8401,13 +8401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45511</v>
+        <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8479,8 +8474,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44879</v>
+        <v>45511</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8552,13 +8552,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8601,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8615,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45666</v>
+        <v>44879</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8628,6 +8623,11 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -8674,7 +8674,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45478</v>
+        <v>45666</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         <v>45477</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45756</v>
+        <v>45478</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45826</v>
+        <v>45756</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45751</v>
+        <v>44845</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44746</v>
+        <v>45302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45029</v>
+        <v>45235</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45701</v>
+        <v>44868</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45078</v>
+        <v>44939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45231</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2431,8 +2431,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45565</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2583,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45302</v>
+        <v>45826</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2656,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45397</v>
+        <v>46098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2734,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45259</v>
+        <v>45314</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44636</v>
+        <v>45161</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2885,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2928,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44923</v>
+        <v>46127</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2952,8 +2957,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3006,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3020,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>45701</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,8 +3035,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3084,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3098,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45544</v>
+        <v>45602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3114,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3157,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3171,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45602</v>
+        <v>45930</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3172,7 +3187,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3230,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3229,10 +3244,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45826</v>
+        <v>45219</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3244,8 +3259,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3308,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3322,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45733</v>
+        <v>44746</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3318,7 +3338,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3361,7 +3381,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3395,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45733</v>
+        <v>45565</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3391,7 +3411,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3434,7 +3454,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3444,14 +3464,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44939</v>
+        <v>45817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3464,7 +3484,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3507,7 +3527,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3521,10 +3541,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46043</v>
+        <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3537,7 +3557,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3580,7 +3600,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3594,10 +3614,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45259</v>
+        <v>45583</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3609,13 +3629,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3673,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3687,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45259</v>
+        <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,13 +3702,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3746,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3760,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45608</v>
+        <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3766,7 +3776,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>16.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3809,7 +3819,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3823,10 +3833,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45583</v>
+        <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3839,7 +3849,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3882,7 +3892,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3896,10 +3906,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44868</v>
+        <v>45259</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3911,8 +3921,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3970,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3969,10 +3984,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45478</v>
+        <v>45733</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3985,7 +4000,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4028,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4042,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45107</v>
+        <v>45733</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4058,7 +4073,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4101,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4115,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45259</v>
+        <v>45161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4130,13 +4145,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4179,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4193,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44945</v>
+        <v>45356</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4209,7 +4219,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4252,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4266,10 +4276,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44882</v>
+        <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4281,13 +4291,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4330,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4344,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45702</v>
+        <v>46167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4359,13 +4364,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4418,14 +4418,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45981</v>
+        <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4437,8 +4437,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4481,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44882</v>
+        <v>45608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4510,13 +4515,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
         <v>45610</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45356</v>
+        <v>44945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45078</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45701</v>
+        <v>46177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46098</v>
+        <v>45702</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4885,8 +4885,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45373</v>
+        <v>45702</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4958,8 +4963,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5012,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5026,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44524</v>
+        <v>45145</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5042,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5085,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5092,7 +5102,7 @@
         <v>45161</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5105,7 +5115,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5158,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5172,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44875</v>
+        <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5193,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5236,14 +5246,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44977</v>
+        <v>45003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5266,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46127</v>
+        <v>46189</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5328,13 +5338,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5377,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45219</v>
+        <v>45478</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5406,13 +5411,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45565</v>
+        <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5484,8 +5484,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5533,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5542,10 +5547,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5563,7 +5568,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5606,7 +5611,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5620,10 +5625,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45817</v>
+        <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5635,8 +5640,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5679,7 +5689,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5693,10 +5703,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45930</v>
+        <v>46246</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5708,8 +5718,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5752,7 +5767,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5762,14 +5777,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44981</v>
+        <v>45981</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5782,7 +5797,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5840,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5835,14 +5850,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44592</v>
+        <v>45107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5855,7 +5870,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5898,7 +5913,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5908,14 +5923,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45369</v>
+        <v>45394</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5928,7 +5943,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5971,7 +5986,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5985,10 +6000,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45161</v>
+        <v>46247</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6001,7 +6016,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6044,7 +6059,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6058,10 +6073,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45356</v>
+        <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6073,8 +6088,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6117,7 +6137,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6131,10 +6151,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46149</v>
+        <v>46260</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6147,7 +6167,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>16.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6190,7 +6210,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6200,14 +6220,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45003</v>
+        <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6220,7 +6240,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6263,7 +6283,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6277,10 +6297,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45062</v>
+        <v>45163</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6293,7 +6313,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6336,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6350,10 +6370,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46167</v>
+        <v>44923</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6366,7 +6386,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6409,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6423,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45145</v>
+        <v>44923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6439,7 +6459,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6482,7 +6502,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6496,10 +6516,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45302</v>
+        <v>45106</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6511,8 +6531,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6555,7 +6580,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6569,10 +6594,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44992</v>
+        <v>45259</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6590,7 +6615,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6633,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6647,10 +6672,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46178</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6668,7 +6693,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6711,7 +6736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6725,10 +6750,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46177</v>
+        <v>45370</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6746,7 +6771,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6789,7 +6814,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6803,10 +6828,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45219</v>
+        <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6824,7 +6849,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6867,7 +6892,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6881,10 +6906,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46189</v>
+        <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6897,7 +6922,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6965,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6950,14 +6975,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45161</v>
+        <v>44592</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6970,7 +6995,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7013,7 +7038,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7027,10 +7052,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45235</v>
+        <v>45302</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7043,7 +7068,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45106</v>
+        <v>44992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7121,7 +7146,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7164,7 +7189,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7178,10 +7203,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45751</v>
+        <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7194,7 +7219,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7237,7 +7262,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7251,10 +7276,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46246</v>
+        <v>46043</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7266,13 +7291,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7315,7 +7335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7329,10 +7349,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46247</v>
+        <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7344,8 +7364,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>9.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7388,7 +7413,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7402,10 +7427,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44845</v>
+        <v>45397</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7418,7 +7443,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7461,7 +7486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7475,10 +7500,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45370</v>
+        <v>45702</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7496,7 +7521,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7564,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7553,10 +7578,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44923</v>
+        <v>44524</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7569,7 +7594,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7612,7 +7637,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7626,10 +7651,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45107</v>
+        <v>45231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7642,7 +7667,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7685,7 +7710,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7699,10 +7724,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45219</v>
+        <v>45078</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7714,13 +7739,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>10.2</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7763,7 +7783,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7777,10 +7797,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45219</v>
+        <v>45356</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7792,13 +7812,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7841,7 +7856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7855,10 +7870,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45163</v>
+        <v>45369</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7871,7 +7886,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7914,7 +7929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7928,10 +7943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46260</v>
+        <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7944,7 +7959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7987,7 +8002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8001,10 +8016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46268</v>
+        <v>45373</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8016,13 +8031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8065,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8082,7 +8092,7 @@
         <v>45702</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8100,7 +8110,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8153,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8167,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45702</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8172,13 +8182,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8226,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8240,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44746</v>
+        <v>45544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8251,7 +8256,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44992</v>
+        <v>45029</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8382,14 +8382,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45394</v>
+        <v>45701</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45511</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44879</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45666</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45478</v>
+        <v>45477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8910,7 +8910,7 @@
         <v>45756</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44845</v>
+        <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45235</v>
+        <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44868</v>
+        <v>45029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44939</v>
+        <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2431,13 +2431,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2553,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2583,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45826</v>
+        <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2656,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46098</v>
+        <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2734,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2807,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45161</v>
+        <v>44636</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2928,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46127</v>
+        <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2957,13 +2952,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3006,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3020,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45701</v>
+        <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3035,13 +3025,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3084,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3098,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45602</v>
+        <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3114,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3157,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3171,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45930</v>
+        <v>45733</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3187,7 +3172,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3230,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3240,14 +3225,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45219</v>
+        <v>44939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3259,13 +3244,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3308,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3322,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44746</v>
+        <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3337,8 +3317,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3381,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3395,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45565</v>
+        <v>45259</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3410,8 +3395,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3454,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3468,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45817</v>
+        <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3484,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3527,7 +3517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3541,10 +3531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45078</v>
+        <v>45583</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3557,7 +3547,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3600,7 +3590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3614,10 +3604,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45583</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3630,7 +3620,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3673,7 +3663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3687,10 +3677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45751</v>
+        <v>45107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3703,7 +3693,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3746,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3760,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46149</v>
+        <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3775,8 +3765,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>16.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3819,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3833,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45751</v>
+        <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3849,7 +3844,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3892,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3906,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45259</v>
+        <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3921,13 +3916,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3970,7 +3960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3984,10 +3974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45733</v>
+        <v>44882</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3999,8 +3989,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4038,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45733</v>
+        <v>45702</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4072,8 +4067,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45161</v>
+        <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4145,8 +4145,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4194,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4208,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45356</v>
+        <v>45610</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4219,7 +4224,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4267,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4281,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45062</v>
+        <v>45356</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4292,7 +4297,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46167</v>
+        <v>45817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4365,7 +4370,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4408,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44992</v>
+        <v>45930</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4437,13 +4442,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45608</v>
+        <v>45078</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45610</v>
+        <v>45602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44945</v>
+        <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4661,8 +4661,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4710,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>45373</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4735,7 +4740,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4783,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4797,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46177</v>
+        <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4807,13 +4812,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45702</v>
+        <v>45161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4885,13 +4885,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4934,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45702</v>
+        <v>46149</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4963,13 +4958,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>16.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5012,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5026,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45145</v>
+        <v>45608</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5042,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5085,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5099,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45161</v>
+        <v>44875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5114,8 +5104,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46178</v>
+        <v>44977</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5187,13 +5182,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5246,14 +5236,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45003</v>
+        <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5263,6 +5253,11 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5309,7 +5304,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5319,14 +5314,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46189</v>
+        <v>45981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5339,7 +5334,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45478</v>
+        <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5411,8 +5406,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45219</v>
+        <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5484,13 +5484,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5533,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5543,14 +5538,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45219</v>
+        <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5562,13 +5557,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5611,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5625,10 +5615,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45219</v>
+        <v>45369</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5640,13 +5630,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5689,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5703,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46246</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5718,13 +5703,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5767,7 +5747,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5777,14 +5757,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45981</v>
+        <v>45356</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5797,7 +5777,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5840,7 +5820,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5854,10 +5834,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45107</v>
+        <v>46167</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5870,7 +5850,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5913,7 +5893,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5927,10 +5907,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45394</v>
+        <v>45003</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5943,7 +5923,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5986,7 +5966,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6000,10 +5980,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46247</v>
+        <v>46034</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6016,7 +5996,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6059,7 +6039,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6073,10 +6053,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44882</v>
+        <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6088,13 +6068,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6137,7 +6112,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6151,10 +6126,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46260</v>
+        <v>45062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6167,7 +6142,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6210,7 +6185,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6224,10 +6199,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44746</v>
+        <v>45145</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6240,7 +6215,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6283,7 +6258,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6297,10 +6272,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45163</v>
+        <v>45302</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6313,7 +6288,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6331,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6370,10 +6345,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44923</v>
+        <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6385,8 +6360,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6429,7 +6409,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6443,10 +6423,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44923</v>
+        <v>46177</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,8 +6438,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6502,7 +6487,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6516,10 +6501,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45106</v>
+        <v>44992</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6537,7 +6522,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6580,7 +6565,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6594,10 +6579,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45259</v>
+        <v>45219</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6615,7 +6600,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6658,7 +6643,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6672,10 +6657,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6687,13 +6672,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6736,7 +6716,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6750,10 +6730,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45370</v>
+        <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6765,13 +6745,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6814,7 +6789,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6828,10 +6803,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44882</v>
+        <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6843,13 +6818,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6892,7 +6862,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6906,10 +6876,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45565</v>
+        <v>45235</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6922,7 +6892,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6965,7 +6935,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6975,14 +6945,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44592</v>
+        <v>45106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6994,8 +6964,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7038,7 +7013,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7052,10 +7027,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45302</v>
+        <v>45751</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7068,7 +7043,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7111,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7125,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44992</v>
+        <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7142,11 +7117,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7189,7 +7164,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7203,10 +7178,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46034</v>
+        <v>44845</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7219,7 +7194,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7262,7 +7237,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7276,10 +7251,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46043</v>
+        <v>46246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7291,8 +7266,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7315,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7329,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45259</v>
+        <v>45370</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7370,7 +7350,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7413,7 +7393,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7427,10 +7407,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45397</v>
+        <v>44923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7443,7 +7423,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7486,7 +7466,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7500,10 +7480,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45702</v>
+        <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7515,13 +7495,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7564,7 +7539,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7578,10 +7553,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44524</v>
+        <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7593,8 +7568,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>10.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7637,7 +7617,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7651,10 +7631,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45231</v>
+        <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7666,8 +7646,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7710,7 +7695,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7724,10 +7709,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45078</v>
+        <v>46247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7740,7 +7725,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7783,7 +7768,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7797,10 +7782,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45356</v>
+        <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7813,7 +7798,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7856,7 +7841,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7870,10 +7855,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45369</v>
+        <v>46260</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7886,7 +7871,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7929,7 +7914,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7943,10 +7928,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45107</v>
+        <v>45702</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7958,8 +7943,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +8006,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45373</v>
+        <v>45702</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8031,8 +8021,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45702</v>
+        <v>44746</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8104,13 +8099,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8153,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8167,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8182,8 +8172,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8236,14 +8231,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45544</v>
+        <v>45394</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8256,7 +8251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45029</v>
+        <v>46268</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8328,8 +8323,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45701</v>
+        <v>45265</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8401,8 +8401,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45265</v>
+        <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8474,13 +8479,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45511</v>
+        <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8552,8 +8552,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8601,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8615,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44879</v>
+        <v>45666</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8623,11 +8628,6 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -8674,7 +8674,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45666</v>
+        <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45477</v>
+        <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45756</v>
+        <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44746</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44636</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45733</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45259</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45583</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44882</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45702</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45610</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>45356</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45930</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45078</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45373</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46149</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45608</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44977</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45369</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45356</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46167</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45003</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>46034</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>45062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45145</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>45302</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>46177</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44992</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45219</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>46189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45235</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45751</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44845</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>46246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45370</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>46247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46260</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45702</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45702</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44746</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45394</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46268</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45265</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45666</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44746</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45701</v>
+        <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45029</v>
+        <v>45701</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44636</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45733</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45259</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44868</v>
+        <v>45583</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45583</v>
+        <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>44868</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3680,7 +3680,7 @@
         <v>45107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44945</v>
+        <v>45565</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45565</v>
+        <v>44945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3960,7 +3960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44882</v>
+        <v>45817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3989,13 +3989,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4038,7 +4033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4052,10 +4047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45702</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4067,13 +4062,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4120,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44882</v>
+        <v>45602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4143,11 +4133,6 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4194,7 +4179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4208,10 +4193,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45610</v>
+        <v>44882</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4221,6 +4206,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4267,7 +4257,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45356</v>
+        <v>45702</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4296,8 +4286,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45817</v>
+        <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4369,8 +4364,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45930</v>
+        <v>45610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45078</v>
+        <v>45356</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45602</v>
+        <v>45078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45701</v>
+        <v>46149</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4661,13 +4661,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4710,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4724,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45373</v>
+        <v>45608</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4740,7 +4735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4783,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4797,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44524</v>
+        <v>45701</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4812,8 +4807,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45161</v>
+        <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46149</v>
+        <v>44524</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>16.7</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45608</v>
+        <v>45161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44875</v>
+        <v>46167</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5104,13 +5104,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5153,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5163,14 +5158,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44977</v>
+        <v>45981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5178,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5221,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5235,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45219</v>
+        <v>44875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5261,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5304,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5314,14 +5309,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45981</v>
+        <v>44977</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5334,7 +5329,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5377,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5391,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5464,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44981</v>
+        <v>46178</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5484,8 +5479,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5538,14 +5538,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44592</v>
+        <v>46177</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5557,8 +5557,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45369</v>
+        <v>45702</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,8 +5635,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5684,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5698,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>46034</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5704,7 +5714,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5747,7 +5757,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5761,10 +5771,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45356</v>
+        <v>44981</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5777,7 +5787,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5820,7 +5830,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5834,10 +5844,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46167</v>
+        <v>46189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5850,7 +5860,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5903,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5903,14 +5913,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45003</v>
+        <v>46043</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5923,7 +5933,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5966,7 +5976,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5976,14 +5986,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46034</v>
+        <v>44592</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5996,7 +6006,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6039,7 +6049,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6053,10 +6063,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46043</v>
+        <v>45369</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6069,7 +6079,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6112,7 +6122,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6126,10 +6136,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45062</v>
+        <v>45161</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6142,7 +6152,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6185,7 +6195,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6199,10 +6209,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45145</v>
+        <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6215,7 +6225,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6258,7 +6268,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6268,14 +6278,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45302</v>
+        <v>45003</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6288,7 +6298,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6331,7 +6341,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6345,10 +6355,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46178</v>
+        <v>46246</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6366,7 +6376,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6409,7 +6419,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6423,10 +6433,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46177</v>
+        <v>46098</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6438,13 +6448,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6487,7 +6492,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6501,10 +6506,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44992</v>
+        <v>45062</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6516,13 +6521,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45219</v>
+        <v>45145</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46189</v>
+        <v>46247</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6673,7 +6668,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6716,7 +6711,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6730,10 +6725,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45161</v>
+        <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6746,7 +6741,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6789,7 +6784,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46098</v>
+        <v>46127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6818,8 +6813,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45235</v>
+        <v>44992</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6891,8 +6891,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6935,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6949,10 +6954,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45106</v>
+        <v>45219</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6970,7 +6975,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7013,7 +7018,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7027,10 +7032,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45751</v>
+        <v>45161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7043,7 +7048,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7091,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7105,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46127</v>
+        <v>45235</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,13 +7120,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7164,7 +7164,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44845</v>
+        <v>45106</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7193,8 +7193,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7237,7 +7242,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7251,10 +7256,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46246</v>
+        <v>45751</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7266,13 +7271,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45370</v>
+        <v>46260</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7344,13 +7344,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7393,7 +7388,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7407,10 +7402,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44923</v>
+        <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7423,7 +7418,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7466,7 +7461,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7480,10 +7475,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45107</v>
+        <v>45370</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7495,8 +7490,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45219</v>
+        <v>44923</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7568,13 +7568,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7617,7 +7612,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7631,10 +7626,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45219</v>
+        <v>46268</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7652,7 +7647,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7695,7 +7690,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7709,10 +7704,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46247</v>
+        <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7725,7 +7720,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7768,7 +7763,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7782,10 +7777,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45163</v>
+        <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7797,8 +7792,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46260</v>
+        <v>45219</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7870,8 +7870,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7914,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7928,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45702</v>
+        <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7943,13 +7948,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8009,7 +8009,7 @@
         <v>45702</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8070,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44746</v>
+        <v>45702</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8099,8 +8099,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44992</v>
+        <v>44746</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8172,13 +8177,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8231,14 +8231,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45394</v>
+        <v>44992</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8250,8 +8250,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8304,14 +8309,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46268</v>
+        <v>45394</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
         <v>45265</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45666</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 53784-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44739</v>
+        <v>44469</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53784-2021</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44469</v>
+        <v>44739</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44472</v>
+        <v>45666</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45751</v>
+        <v>45219</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,8 +2066,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2115,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44746</v>
+        <v>44472</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2145,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2188,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2202,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45029</v>
+        <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2218,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2261,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45701</v>
+        <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2291,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45078</v>
+        <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2364,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45231</v>
+        <v>44845</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45565</v>
+        <v>45078</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,13 +2582,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45397</v>
+        <v>45751</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45259</v>
+        <v>45751</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,13 +2801,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44636</v>
+        <v>45756</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44923</v>
+        <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2952,8 +2947,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45544</v>
+        <v>45733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3086,7 +3086,7 @@
         <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45733</v>
+        <v>45161</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44939</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45259</v>
+        <v>45602</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3315,11 +3315,6 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3366,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45259</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3395,13 +3390,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3434,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3448,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45583</v>
+        <v>45235</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3464,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3507,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3521,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>44868</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3547,7 +3537,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3590,7 +3580,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3604,10 +3594,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44868</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3619,8 +3609,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3663,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45107</v>
+        <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3693,7 +3688,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3731,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45259</v>
+        <v>44945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3765,13 +3760,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3814,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45565</v>
+        <v>44981</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3844,7 +3834,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44945</v>
+        <v>45702</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3916,8 +3906,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3960,7 +3955,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45817</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3989,8 +3984,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45602</v>
+        <v>45161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44882</v>
+        <v>44875</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4267,14 +4267,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45702</v>
+        <v>45003</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4286,13 +4286,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4330,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4345,14 +4340,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44882</v>
+        <v>44939</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4364,13 +4359,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4403,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4417,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45610</v>
+        <v>44636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4433,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4476,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4490,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45356</v>
+        <v>45608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4506,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4549,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4563,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45078</v>
+        <v>45478</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4589,7 +4579,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4632,7 +4622,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4636,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46149</v>
+        <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4661,8 +4651,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>16.7</v>
+        <v>10.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45608</v>
+        <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4734,8 +4729,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45701</v>
+        <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45373</v>
+        <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4885,8 +4885,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44524</v>
+        <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4964,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45161</v>
+        <v>45314</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5031,8 +5036,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5085,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5085,14 +5095,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46167</v>
+        <v>45394</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5105,7 +5115,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5165,7 +5175,7 @@
         <v>45981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5221,7 +5231,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5235,10 +5245,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44875</v>
+        <v>45161</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5250,13 +5260,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5304,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5318,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44977</v>
+        <v>45701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5326,6 +5331,11 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -5372,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45219</v>
+        <v>46034</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5401,13 +5411,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5450,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5464,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46178</v>
+        <v>44882</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5485,7 +5490,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5533,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5542,10 +5547,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46177</v>
+        <v>44746</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5557,13 +5562,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45702</v>
+        <v>45163</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5635,13 +5635,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5684,7 +5679,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5698,10 +5693,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46034</v>
+        <v>44923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5714,7 +5709,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5757,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5771,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44981</v>
+        <v>44923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5787,7 +5782,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5830,7 +5825,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5844,10 +5839,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46189</v>
+        <v>46043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5860,7 +5855,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5903,7 +5898,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5917,10 +5912,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46043</v>
+        <v>45106</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5932,8 +5927,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5986,14 +5986,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44592</v>
+        <v>45259</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6005,8 +6005,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6049,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6078,8 +6083,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6122,7 +6132,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6136,10 +6146,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45161</v>
+        <v>44882</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6151,8 +6161,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6195,7 +6210,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6209,10 +6224,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45356</v>
+        <v>45565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6225,7 +6240,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6268,7 +6283,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6278,14 +6293,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45003</v>
+        <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6298,7 +6313,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6341,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6351,14 +6366,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46246</v>
+        <v>44592</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6370,13 +6385,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6419,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6433,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46098</v>
+        <v>46246</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6448,8 +6458,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6492,7 +6507,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6506,10 +6521,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45062</v>
+        <v>45302</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6522,7 +6537,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6565,7 +6580,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6579,10 +6594,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45145</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6594,8 +6609,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6638,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6652,10 +6672,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46247</v>
+        <v>46098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6668,7 +6688,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>9.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6711,7 +6731,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6725,10 +6745,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45302</v>
+        <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6740,8 +6760,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6784,7 +6809,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6798,10 +6823,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46127</v>
+        <v>45397</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6813,13 +6838,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6862,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6876,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44992</v>
+        <v>46127</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6893,11 +6913,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6960,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6954,10 +6974,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45219</v>
+        <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6975,7 +6995,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7018,7 +7038,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7032,10 +7052,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45161</v>
+        <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7048,7 +7068,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7091,7 +7111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7105,10 +7125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45235</v>
+        <v>45231</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7121,7 +7141,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7164,7 +7184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7178,10 +7198,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45106</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7193,13 +7213,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7242,7 +7257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7256,10 +7271,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45751</v>
+        <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7272,7 +7287,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7315,7 +7330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7329,10 +7344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46260</v>
+        <v>45356</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7345,7 +7360,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7388,7 +7403,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7402,10 +7417,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44845</v>
+        <v>45369</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7418,7 +7433,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7461,7 +7476,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7475,10 +7490,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45370</v>
+        <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7490,13 +7505,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7539,7 +7549,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7553,10 +7563,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44923</v>
+        <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7569,7 +7579,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7612,7 +7622,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7626,10 +7636,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46268</v>
+        <v>45702</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7647,7 +7657,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7690,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7704,10 +7714,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45107</v>
+        <v>45565</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7720,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7763,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7777,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45219</v>
+        <v>45817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7792,13 +7802,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>10.2</v>
+        <v>6.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7841,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7855,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45219</v>
+        <v>44977</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7870,13 +7875,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45163</v>
+        <v>45544</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45702</v>
+        <v>45029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8021,13 +8021,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8070,7 +8065,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8084,10 +8079,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45702</v>
+        <v>45701</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8099,13 +8094,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44746</v>
+        <v>46149</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8168,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>16.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44992</v>
+        <v>45265</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8256,7 +8246,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8289,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8309,14 +8299,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45394</v>
+        <v>45511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8329,7 +8319,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8362,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8376,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45265</v>
+        <v>44879</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8407,7 +8397,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45511</v>
+        <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8513,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8527,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44879</v>
+        <v>46177</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8558,7 +8548,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8601,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8615,10 +8605,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45666</v>
+        <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8630,8 +8620,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8674,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8688,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45477</v>
+        <v>46189</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8704,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8747,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45478</v>
+        <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8777,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45756</v>
+        <v>46260</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45826</v>
+        <v>46268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8922,8 +8917,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53784-2021</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44469</v>
+        <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 53784-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44739</v>
+        <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45666</v>
+        <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45219</v>
+        <v>44746</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,13 +2066,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2115,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44472</v>
+        <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2145,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2188,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2202,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45478</v>
+        <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2218,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2261,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44746</v>
+        <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2291,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45477</v>
+        <v>45231</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2364,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44845</v>
+        <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2437,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45078</v>
+        <v>45751</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2553,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45583</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,8 +2577,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>45302</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45751</v>
+        <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45751</v>
+        <v>45259</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,8 +2801,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45756</v>
+        <v>44636</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45259</v>
+        <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,13 +2952,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45733</v>
+        <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3086,7 +3086,7 @@
         <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45161</v>
+        <v>45733</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>44939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45602</v>
+        <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3315,6 +3315,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3361,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>45259</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3390,8 +3395,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3434,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3448,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45235</v>
+        <v>45583</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3464,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3524,7 +3534,7 @@
         <v>44868</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3580,7 +3590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3594,10 +3604,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3609,13 +3619,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45610</v>
+        <v>45107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3688,7 +3693,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3731,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44945</v>
+        <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,8 +3765,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44981</v>
+        <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3834,7 +3844,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45702</v>
+        <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3906,13 +3916,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3969,10 +3974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3984,13 +3989,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45145</v>
+        <v>44882</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4062,8 +4062,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4106,7 +4111,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4120,10 +4125,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45161</v>
+        <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4135,8 +4140,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4179,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4193,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44875</v>
+        <v>44882</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4214,7 +4224,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4257,7 +4267,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4267,14 +4277,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45003</v>
+        <v>45610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4287,7 +4297,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4330,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4340,14 +4350,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44939</v>
+        <v>45356</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4360,7 +4370,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4403,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4417,10 +4427,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44636</v>
+        <v>45078</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4433,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4476,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4490,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45608</v>
+        <v>45817</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4506,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4549,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4563,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45478</v>
+        <v>45930</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4579,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4622,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4636,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45219</v>
+        <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4657,7 +4667,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4700,7 +4710,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4714,10 +4724,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45219</v>
+        <v>45608</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4729,13 +4739,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4783,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4797,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45259</v>
+        <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4807,13 +4812,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45219</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4885,13 +4885,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4934,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45107</v>
+        <v>45161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4964,7 +4959,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5007,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5021,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45314</v>
+        <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5042,7 +5037,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5085,7 +5080,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5095,14 +5090,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45394</v>
+        <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5115,7 +5110,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5168,14 +5163,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45981</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5187,8 +5182,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45161</v>
+        <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45701</v>
+        <v>46149</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5333,13 +5333,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46034</v>
+        <v>45702</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5411,8 +5406,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44882</v>
+        <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5484,13 +5484,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5533,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44746</v>
+        <v>46034</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5563,7 +5558,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5606,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5616,14 +5611,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45163</v>
+        <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5636,7 +5631,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5679,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5693,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44923</v>
+        <v>45369</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5709,7 +5704,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5752,7 +5747,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5766,10 +5761,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44923</v>
+        <v>46043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5782,7 +5777,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5820,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5839,10 +5834,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46043</v>
+        <v>46167</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5855,7 +5850,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5898,7 +5893,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5912,10 +5907,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45106</v>
+        <v>45161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5927,13 +5922,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5976,7 +5966,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5990,10 +5980,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45259</v>
+        <v>45356</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6005,13 +5995,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6039,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6064,14 +6049,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45370</v>
+        <v>45003</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6081,11 +6066,6 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6132,7 +6112,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6146,10 +6126,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44882</v>
+        <v>45062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,13 +6141,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6210,7 +6185,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6224,10 +6199,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45565</v>
+        <v>46098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6240,7 +6215,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6283,7 +6258,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6297,10 +6272,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45826</v>
+        <v>46178</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6312,8 +6287,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6336,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6366,14 +6346,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44592</v>
+        <v>46177</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6385,8 +6365,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6429,7 +6414,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6443,10 +6428,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46246</v>
+        <v>46189</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,13 +6443,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6507,7 +6487,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6521,10 +6501,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45302</v>
+        <v>45145</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6537,7 +6517,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6580,7 +6560,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6594,10 +6574,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44992</v>
+        <v>45302</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6609,13 +6589,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6658,7 +6633,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6672,10 +6647,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46098</v>
+        <v>44992</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6687,8 +6662,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6731,7 +6711,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6745,10 +6725,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45259</v>
+        <v>46127</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6762,11 +6742,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6809,7 +6789,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6823,10 +6803,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45397</v>
+        <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6838,8 +6818,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6867,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6881,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46127</v>
+        <v>45161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6911,13 +6896,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6960,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6974,10 +6954,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45702</v>
+        <v>45235</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6989,13 +6969,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7038,7 +7013,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7052,10 +7027,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44524</v>
+        <v>46247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7068,7 +7043,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7111,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7125,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45231</v>
+        <v>45106</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7140,8 +7115,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7184,7 +7164,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7198,10 +7178,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45930</v>
+        <v>45751</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7214,7 +7194,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7257,7 +7237,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7271,10 +7251,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45078</v>
+        <v>44845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7287,7 +7267,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7330,7 +7310,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7344,10 +7324,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45356</v>
+        <v>45370</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7359,8 +7339,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7403,7 +7388,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7417,10 +7402,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45369</v>
+        <v>44923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7433,7 +7418,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7493,7 +7478,7 @@
         <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7549,7 +7534,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7563,10 +7548,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45373</v>
+        <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7578,8 +7563,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>10.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7622,7 +7612,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7636,10 +7626,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7657,7 +7647,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7700,7 +7690,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7714,10 +7704,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45565</v>
+        <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7730,7 +7720,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7763,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7777,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45817</v>
+        <v>46260</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7803,7 +7793,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7846,7 +7836,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7860,10 +7850,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44977</v>
+        <v>46268</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7875,8 +7865,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7914,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,10 +7928,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45544</v>
+        <v>45702</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7948,8 +7943,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45029</v>
+        <v>45702</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8021,8 +8021,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8065,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8079,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45701</v>
+        <v>44746</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8095,7 +8100,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8138,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8152,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46149</v>
+        <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8167,8 +8172,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>16.7</v>
+        <v>6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8211,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8221,14 +8231,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45265</v>
+        <v>45394</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8240,13 +8250,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45511</v>
+        <v>45265</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8318,8 +8323,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8362,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8376,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44879</v>
+        <v>45511</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8391,13 +8401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46167</v>
+        <v>44879</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8469,8 +8474,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8513,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8527,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46177</v>
+        <v>45666</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8542,13 +8552,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8605,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46178</v>
+        <v>45477</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8620,13 +8625,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46189</v>
+        <v>45478</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,8 +8771,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8829,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46260</v>
+        <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8845,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8888,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8902,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46268</v>
+        <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8917,13 +8922,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44746</v>
+        <v>44845</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45701</v>
+        <v>45302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45029</v>
+        <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45078</v>
+        <v>45235</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45231</v>
+        <v>46034</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45565</v>
+        <v>44868</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45751</v>
+        <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,13 +2577,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2621,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2635,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45302</v>
+        <v>44875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,8 +2650,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45397</v>
+        <v>44939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45259</v>
+        <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,13 +2801,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44636</v>
+        <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44923</v>
+        <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2952,8 +2947,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45544</v>
+        <v>45608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45733</v>
+        <v>45314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3098,8 +3098,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45733</v>
+        <v>46127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,8 +3176,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3225,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3225,14 +3235,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44939</v>
+        <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3255,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3298,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3298,14 +3308,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45259</v>
+        <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3317,13 +3327,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3371,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3385,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45259</v>
+        <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3406,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3449,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3463,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45583</v>
+        <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3479,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3522,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3536,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44868</v>
+        <v>45219</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3546,8 +3551,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3590,7 +3600,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3604,10 +3614,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3620,7 +3630,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3663,7 +3673,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3677,10 +3687,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45107</v>
+        <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3693,7 +3703,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3746,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3760,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45259</v>
+        <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3765,13 +3775,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3814,7 +3819,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3833,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44945</v>
+        <v>45078</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3844,7 +3849,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3892,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45565</v>
+        <v>45583</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3917,7 +3922,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3960,7 +3965,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45602</v>
+        <v>46149</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3990,7 +3995,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4033,7 +4038,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4047,10 +4052,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44882</v>
+        <v>45751</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4062,13 +4067,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45702</v>
+        <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4140,13 +4140,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4184,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4198,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44882</v>
+        <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4224,7 +4219,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4267,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4281,10 +4276,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45610</v>
+        <v>45733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4297,7 +4292,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45356</v>
+        <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4370,7 +4365,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45078</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4438,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45817</v>
+        <v>45826</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4511,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45930</v>
+        <v>45356</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4589,7 +4584,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4632,7 +4627,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4641,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45701</v>
+        <v>46167</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4661,13 +4656,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4710,7 +4700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4724,10 +4714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45608</v>
+        <v>45062</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4740,7 +4730,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4783,7 +4773,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4797,10 +4787,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45373</v>
+        <v>44992</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4812,8 +4802,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45161</v>
+        <v>46177</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4958,8 +4953,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44875</v>
+        <v>44945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5031,13 +5031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5080,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5094,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44977</v>
+        <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5110,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5153,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5167,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5188,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5231,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5241,14 +5236,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45981</v>
+        <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5260,8 +5255,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46149</v>
+        <v>45702</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5333,8 +5333,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>16.7</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5377,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45702</v>
+        <v>45145</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5404,11 +5409,6 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5455,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44981</v>
+        <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46034</v>
+        <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44592</v>
+        <v>45003</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45369</v>
+        <v>45478</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46043</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5776,8 +5776,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5820,7 +5825,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5834,10 +5839,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46167</v>
+        <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5849,8 +5854,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5903,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5907,10 +5917,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45161</v>
+        <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5922,8 +5932,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5966,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5980,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5996,7 +6011,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6039,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6049,14 +6064,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45003</v>
+        <v>46260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6069,7 +6084,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6112,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6122,14 +6137,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45062</v>
+        <v>45394</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6142,7 +6157,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6185,7 +6200,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6199,10 +6214,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46098</v>
+        <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6214,8 +6229,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6258,7 +6278,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6272,10 +6292,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46178</v>
+        <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6293,7 +6313,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6336,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6350,10 +6370,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46177</v>
+        <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6365,13 +6385,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6414,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6428,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46189</v>
+        <v>45163</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6444,7 +6459,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6487,7 +6502,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6501,10 +6516,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45145</v>
+        <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6517,7 +6532,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6560,7 +6575,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6574,10 +6589,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45302</v>
+        <v>44923</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6590,7 +6605,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6633,7 +6648,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6647,10 +6662,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44992</v>
+        <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6668,7 +6683,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6711,7 +6726,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6725,10 +6740,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46127</v>
+        <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6742,11 +6757,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6789,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6803,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45219</v>
+        <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6824,7 +6839,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6867,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6881,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45161</v>
+        <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6896,8 +6911,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6960,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6954,10 +6974,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45235</v>
+        <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6970,7 +6990,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7013,7 +7033,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7023,14 +7043,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46247</v>
+        <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7043,7 +7063,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45106</v>
+        <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,13 +7135,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7164,7 +7179,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7178,10 +7193,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45751</v>
+        <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7194,7 +7209,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7237,7 +7252,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7251,10 +7266,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44845</v>
+        <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7266,8 +7281,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7310,7 +7330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7324,10 +7344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45370</v>
+        <v>46246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7345,7 +7365,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7388,7 +7408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7402,10 +7422,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44923</v>
+        <v>45259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7415,6 +7435,11 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -7461,7 +7486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7475,10 +7500,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45107</v>
+        <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7491,7 +7516,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7534,7 +7559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7548,10 +7573,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45219</v>
+        <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7569,7 +7594,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7612,7 +7637,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7626,10 +7651,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45219</v>
+        <v>44524</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7641,13 +7666,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7690,7 +7710,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7704,10 +7724,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45163</v>
+        <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7720,7 +7740,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7763,7 +7783,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7777,10 +7797,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46260</v>
+        <v>45078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7793,7 +7813,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7836,7 +7856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7850,10 +7870,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46268</v>
+        <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7865,13 +7885,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7914,7 +7929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7928,10 +7943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45702</v>
+        <v>45369</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7943,13 +7958,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +8002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8006,10 +8016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45702</v>
+        <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8021,13 +8031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8084,10 +8089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44746</v>
+        <v>45373</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44992</v>
+        <v>45702</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8183,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8226,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8231,14 +8236,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45394</v>
+        <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8251,7 +8256,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45265</v>
+        <v>45544</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45511</v>
+        <v>45029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44879</v>
+        <v>45701</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8474,13 +8474,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45666</v>
+        <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8552,8 +8547,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45477</v>
+        <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45478</v>
+        <v>44879</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8698,8 +8698,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8747,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8761,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46246</v>
+        <v>45666</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,13 +8776,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45756</v>
+        <v>45478</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45826</v>
+        <v>45477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44845</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45235</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46034</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44868</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>44939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45219</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45078</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45583</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46149</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45751</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45826</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45356</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46167</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45062</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44992</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46177</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45702</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45145</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45003</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45478</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45394</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45163</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44923</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>46246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44524</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45369</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45373</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45702</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45544</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45701</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44879</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45666</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45478</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44467</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44472</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44845</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45235</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46034</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44868</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>44939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45219</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44746</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45078</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45583</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46149</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45751</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45826</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45356</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46167</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45062</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44992</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46177</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45702</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45145</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45003</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45478</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45394</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45163</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44923</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>46246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45397</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44524</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45369</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45373</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45702</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45544</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45701</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44879</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45666</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45478</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45434</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44858</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45582</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45709</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45901</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46043</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46136</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46213</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE145"/>
+  <dimension ref="A1:AE144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52729-2021</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44467</v>
+        <v>44472</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44472</v>
+        <v>45751</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44845</v>
+        <v>45701</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45756</v>
+        <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45235</v>
+        <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46034</v>
+        <v>45231</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44868</v>
+        <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46043</v>
+        <v>45666</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45602</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,8 +2577,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2621,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2635,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44875</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2650,13 +2655,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44939</v>
+        <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44636</v>
+        <v>45756</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46098</v>
+        <v>45302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45259</v>
+        <v>45397</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,13 +2947,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2991,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45608</v>
+        <v>45602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3104,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46127</v>
+        <v>44636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3176,13 +3171,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3225,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3239,10 +3229,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45161</v>
+        <v>44923</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3255,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3298,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3308,14 +3298,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45981</v>
+        <v>45544</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3328,7 +3318,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3371,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45701</v>
+        <v>45608</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3400,13 +3390,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3449,7 +3434,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3463,10 +3448,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45930</v>
+        <v>45826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3479,7 +3464,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3522,7 +3507,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3536,10 +3521,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45219</v>
+        <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3551,13 +3536,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3600,7 +3580,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3614,10 +3594,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45565</v>
+        <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3630,7 +3610,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3673,7 +3653,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3687,10 +3667,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45817</v>
+        <v>46034</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3703,7 +3683,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3746,7 +3726,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3756,14 +3736,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44746</v>
+        <v>44939</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3776,7 +3756,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3819,7 +3799,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3833,10 +3813,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45078</v>
+        <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3846,6 +3826,11 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3892,7 +3877,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3906,10 +3891,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45583</v>
+        <v>45259</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3921,8 +3906,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3965,7 +3955,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3979,10 +3969,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46149</v>
+        <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3995,7 +3985,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>16.7</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4038,7 +4028,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4052,10 +4042,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45751</v>
+        <v>45583</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4068,7 +4058,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4111,7 +4101,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4125,10 +4115,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45751</v>
+        <v>44868</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4141,7 +4131,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,7 +4174,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4194,14 +4184,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45259</v>
+        <v>45981</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4213,13 +4203,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4247,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4261,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45733</v>
+        <v>45478</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4292,7 +4277,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4320,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,10 +4334,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45733</v>
+        <v>45107</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4365,7 +4350,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4408,7 +4393,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,10 +4407,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4437,8 +4422,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4481,7 +4471,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4495,10 +4485,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45826</v>
+        <v>44945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4511,7 +4501,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4554,7 +4544,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4568,10 +4558,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45356</v>
+        <v>44882</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4583,8 +4573,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4627,7 +4622,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4641,10 +4636,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46167</v>
+        <v>45702</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4656,8 +4651,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45062</v>
+        <v>44882</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4729,8 +4729,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4773,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44992</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4802,13 +4807,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45356</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46177</v>
+        <v>45078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4953,13 +4953,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +4997,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5011,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44945</v>
+        <v>45701</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5031,8 +5026,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44981</v>
+        <v>46098</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46178</v>
+        <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5177,13 +5177,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5221,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5235,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45702</v>
+        <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5255,13 +5250,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5304,7 +5294,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5318,10 +5308,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45702</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5333,13 +5323,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5367,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5381,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45145</v>
+        <v>44875</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5411,8 +5396,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5455,7 +5445,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5469,10 +5459,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45161</v>
+        <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5485,7 +5475,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5518,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5542,10 +5532,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46189</v>
+        <v>46127</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5557,8 +5547,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5596,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5611,14 +5606,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45003</v>
+        <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5628,6 +5623,11 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5674,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45478</v>
+        <v>45565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5776,13 +5776,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>10.2</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5820,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5839,10 +5834,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45219</v>
+        <v>45930</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5854,13 +5849,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5903,7 +5893,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5917,10 +5907,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45219</v>
+        <v>45702</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5981,7 +5971,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5985,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45107</v>
+        <v>44981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6011,7 +6001,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6044,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6064,14 +6054,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46260</v>
+        <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6084,7 +6074,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6127,7 +6117,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6137,14 +6127,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45394</v>
+        <v>45369</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6157,7 +6147,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6200,7 +6190,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6214,10 +6204,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44882</v>
+        <v>46149</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6229,13 +6219,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6278,7 +6263,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6292,10 +6277,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46268</v>
+        <v>45161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6307,13 +6292,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6336,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6370,10 +6350,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44746</v>
+        <v>45356</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6386,7 +6366,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6429,7 +6409,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6439,14 +6419,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45163</v>
+        <v>45003</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6459,7 +6439,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6502,7 +6482,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6516,10 +6496,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44923</v>
+        <v>46167</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6532,7 +6512,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6575,7 +6555,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6589,10 +6569,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44923</v>
+        <v>45062</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6605,7 +6585,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6648,7 +6628,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6662,10 +6642,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45106</v>
+        <v>45145</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6677,13 +6657,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6726,7 +6701,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6740,10 +6715,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45259</v>
+        <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6755,13 +6730,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6804,7 +6774,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6818,10 +6788,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45370</v>
+        <v>46178</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6839,7 +6809,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6852,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6866,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44882</v>
+        <v>44992</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6917,7 +6887,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6960,7 +6930,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6974,10 +6944,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45565</v>
+        <v>46177</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6989,8 +6959,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7033,7 +7008,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7043,14 +7018,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44592</v>
+        <v>45219</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7062,8 +7037,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45302</v>
+        <v>46189</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7136,7 +7116,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7179,7 +7159,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7193,10 +7173,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46247</v>
+        <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7209,7 +7189,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>9.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7252,7 +7232,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7266,10 +7246,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44992</v>
+        <v>45235</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7281,13 +7261,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7330,7 +7305,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7344,10 +7319,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46246</v>
+        <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7365,7 +7340,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7408,7 +7383,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7422,10 +7397,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45259</v>
+        <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7437,13 +7412,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7486,7 +7456,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7500,10 +7470,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45397</v>
+        <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7516,7 +7486,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7559,7 +7529,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7573,10 +7543,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45702</v>
+        <v>45370</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7594,7 +7564,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7637,7 +7607,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7651,10 +7621,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44524</v>
+        <v>44923</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7667,7 +7637,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7710,7 +7680,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7724,10 +7694,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45231</v>
+        <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7740,7 +7710,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7783,7 +7753,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7797,10 +7767,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45078</v>
+        <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7812,8 +7782,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>4.3</v>
+        <v>10.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7856,7 +7831,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7870,10 +7845,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45356</v>
+        <v>45219</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7885,8 +7860,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7929,7 +7909,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7943,10 +7923,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45369</v>
+        <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7959,7 +7939,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7982,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +7996,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45107</v>
+        <v>46260</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8032,7 +8012,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8055,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8069,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45373</v>
+        <v>46268</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8104,8 +8084,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8133,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8165,7 +8150,7 @@
         <v>45702</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8183,7 +8168,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8211,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8240,10 +8225,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44977</v>
+        <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8255,8 +8240,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8289,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8303,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45544</v>
+        <v>44746</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8329,7 +8319,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8362,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8376,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45029</v>
+        <v>44992</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8401,8 +8391,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8455,14 +8450,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45701</v>
+        <v>45394</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8475,7 +8470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8535,7 +8530,7 @@
         <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8608,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8681,7 @@
         <v>44879</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8747,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45666</v>
+        <v>46246</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8776,8 +8771,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45478</v>
+        <v>46247</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,24 +8893,24 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45477</v>
+        <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8976,14 +8976,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44637</v>
+        <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8995,8 +8995,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9039,7 +9044,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9053,10 +9058,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45434</v>
+        <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9068,13 +9073,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9131,10 +9131,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44918</v>
+        <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>10.7</v>
+        <v>44.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44830</v>
+        <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>44.5</v>
+        <v>17.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9263,7 +9263,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44543</v>
+        <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9346,14 +9346,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44988</v>
+        <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45565</v>
+        <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45348</v>
+        <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>15.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44858</v>
+        <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>15.8</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45608</v>
+        <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9657,8 +9657,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9701,7 +9706,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9715,10 +9720,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45434</v>
+        <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9730,13 +9735,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9779,7 +9779,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44988</v>
+        <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9866,10 +9866,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45582</v>
+        <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13.8</v>
+        <v>40.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9925,7 +9925,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9939,10 +9939,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44936</v>
+        <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>40.1</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45607</v>
+        <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4</v>
+        <v>55.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44936</v>
+        <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>55.2</v>
+        <v>13.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10144,7 +10144,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45393</v>
+        <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10217,7 +10217,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45002</v>
+        <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>12.7</v>
+        <v>11.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10290,7 +10290,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10304,10 +10304,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45608</v>
+        <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>11.6</v>
+        <v>31.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45709</v>
+        <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>31.1</v>
+        <v>15.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45901</v>
+        <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>15.1</v>
+        <v>5.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46030</v>
+        <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10538,8 +10538,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10582,7 +10587,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10596,10 +10601,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10617,7 +10622,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>20</v>
+        <v>21.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10660,7 +10665,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10677,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10695,7 +10700,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10738,7 +10743,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10755,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10773,7 +10778,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>19.8</v>
+        <v>5.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10816,7 +10821,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10833,7 +10838,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10851,7 +10856,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10894,7 +10899,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10923,13 +10928,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>8.199999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46058</v>
+        <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>27.6</v>
+        <v>8.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46136</v>
+        <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11074,8 +11074,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11118,7 +11123,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11135,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11153,7 +11158,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>11.1</v>
+        <v>17.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11196,7 +11201,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11213,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11231,7 +11236,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>17.7</v>
+        <v>28.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11274,7 +11279,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11291,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11309,7 +11314,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>28.1</v>
+        <v>15.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11352,7 +11357,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S 2015-2026</t>
+          <t>S 2017-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11369,7 +11374,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11387,7 +11392,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11427,10 +11432,10 @@
       </c>
       <c r="V143" s="2" t="inlineStr"/>
     </row>
-    <row r="144" ht="15" customHeight="1">
+    <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S 2017-2026</t>
+          <t>S 2047-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11444,10 +11449,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11465,7 +11470,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11504,84 +11509,6 @@
         <v>0</v>
       </c>
       <c r="V144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>S 2047-2026</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D145" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E145" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I145" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44472</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45751</v>
+        <v>44845</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45701</v>
+        <v>45302</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44746</v>
+        <v>45478</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45029</v>
+        <v>45477</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45078</v>
+        <v>45756</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45231</v>
+        <v>45235</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45565</v>
+        <v>44868</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45666</v>
+        <v>45602</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>46034</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,13 +2577,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2621,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2635,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>44875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,8 +2650,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45478</v>
+        <v>44939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45756</v>
+        <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45302</v>
+        <v>46043</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45397</v>
+        <v>45826</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45602</v>
+        <v>45259</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3018,6 +3018,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3064,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45259</v>
+        <v>45608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,13 +3098,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44636</v>
+        <v>45314</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,8 +3171,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3229,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44923</v>
+        <v>45161</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3250,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3298,14 +3303,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45544</v>
+        <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3318,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45608</v>
+        <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3390,8 +3395,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3434,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3448,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45826</v>
+        <v>45219</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3463,8 +3473,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3507,7 +3522,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3521,10 +3536,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45733</v>
+        <v>46098</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3537,7 +3552,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3580,7 +3595,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3594,10 +3609,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45733</v>
+        <v>44746</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3610,7 +3625,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3653,7 +3668,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3667,10 +3682,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46034</v>
+        <v>45078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3683,7 +3698,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3726,7 +3741,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3736,14 +3751,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44939</v>
+        <v>45583</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3756,7 +3771,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3799,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3813,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45259</v>
+        <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3826,11 +3841,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3877,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3891,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45259</v>
+        <v>46127</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3908,11 +3918,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3965,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3969,10 +3979,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46043</v>
+        <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3985,7 +3995,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4028,7 +4038,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4042,10 +4052,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45583</v>
+        <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4057,8 +4067,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4101,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4115,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44868</v>
+        <v>45733</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4131,7 +4146,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4174,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4184,14 +4199,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45981</v>
+        <v>45733</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4204,7 +4219,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4247,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4261,10 +4276,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45478</v>
+        <v>45161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4277,7 +4292,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4320,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4334,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4350,7 +4365,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4393,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4407,10 +4422,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45259</v>
+        <v>45930</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4422,13 +4437,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4471,7 +4481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4485,10 +4495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44945</v>
+        <v>45062</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4501,7 +4511,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4544,7 +4554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4558,10 +4568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44882</v>
+        <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4579,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4622,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4636,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45702</v>
+        <v>45610</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4651,13 +4661,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44882</v>
+        <v>45565</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4729,13 +4734,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45356</v>
+        <v>45817</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45078</v>
+        <v>44981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46098</v>
+        <v>45702</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5104,8 +5104,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5153,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5167,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45373</v>
+        <v>45145</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5178,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5221,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5235,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44524</v>
+        <v>45161</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5251,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5294,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5304,14 +5309,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>45003</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5324,7 +5329,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5367,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5381,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44875</v>
+        <v>45478</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5396,13 +5401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44977</v>
+        <v>46149</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46127</v>
+        <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5613,7 +5613,7 @@
         <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45565</v>
+        <v>45219</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5703,8 +5703,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5747,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45817</v>
+        <v>45107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5777,7 +5782,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5820,7 +5825,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5834,10 +5839,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45930</v>
+        <v>46167</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5850,7 +5855,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5898,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5903,14 +5908,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45702</v>
+        <v>45394</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5922,13 +5927,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44981</v>
+        <v>46177</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6000,8 +6000,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6044,7 +6049,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6054,14 +6059,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44592</v>
+        <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6073,8 +6078,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6117,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6131,10 +6141,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45369</v>
+        <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6146,8 +6156,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6190,7 +6205,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6204,10 +6219,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46149</v>
+        <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6220,7 +6235,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>16.7</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6263,7 +6278,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6277,10 +6292,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45161</v>
+        <v>45163</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6293,7 +6308,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6336,7 +6351,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6350,10 +6365,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45356</v>
+        <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6366,7 +6381,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6409,7 +6424,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6419,14 +6434,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45003</v>
+        <v>44923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6439,7 +6454,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6482,7 +6497,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6496,10 +6511,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46167</v>
+        <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6512,7 +6527,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6555,7 +6570,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6569,10 +6584,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45062</v>
+        <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6584,8 +6599,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6628,7 +6648,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6642,10 +6662,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45145</v>
+        <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6657,8 +6677,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6701,7 +6726,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6715,10 +6740,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45302</v>
+        <v>45370</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6730,8 +6755,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6774,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6788,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46178</v>
+        <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6809,7 +6839,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6852,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6866,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44992</v>
+        <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6881,13 +6911,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6930,7 +6955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6940,14 +6965,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46177</v>
+        <v>44592</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6959,13 +6984,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7008,7 +7028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7022,10 +7042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45219</v>
+        <v>45302</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7037,13 +7057,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7101,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7115,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46189</v>
+        <v>44992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,8 +7130,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7159,7 +7179,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7173,10 +7193,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45161</v>
+        <v>46260</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7189,7 +7209,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7232,7 +7252,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7246,10 +7266,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45235</v>
+        <v>45259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7261,8 +7281,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7305,7 +7330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7319,10 +7344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45106</v>
+        <v>45397</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7334,13 +7359,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7383,7 +7403,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7397,10 +7417,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45751</v>
+        <v>46268</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7412,8 +7432,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7456,7 +7481,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7470,10 +7495,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44845</v>
+        <v>45702</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7485,8 +7510,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7529,7 +7559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7543,10 +7573,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45370</v>
+        <v>44524</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7558,13 +7588,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7607,7 +7632,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7621,10 +7646,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44923</v>
+        <v>45231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7637,7 +7662,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7680,7 +7705,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7694,10 +7719,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45107</v>
+        <v>45078</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7710,7 +7735,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7753,7 +7778,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7767,10 +7792,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45219</v>
+        <v>45356</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7782,13 +7807,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>10.2</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7831,7 +7851,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7845,10 +7865,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45219</v>
+        <v>45369</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7860,13 +7880,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7909,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7923,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45163</v>
+        <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7939,7 +7954,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7982,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7996,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46260</v>
+        <v>45373</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8012,7 +8027,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8055,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8069,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46268</v>
+        <v>45702</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8090,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8133,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8147,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45702</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8162,13 +8177,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8211,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8225,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45702</v>
+        <v>45544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8240,13 +8250,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44746</v>
+        <v>45029</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44992</v>
+        <v>45701</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8391,13 +8396,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45394</v>
+        <v>46247</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44879</v>
+        <v>46246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46246</v>
+        <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46247</v>
+        <v>45666</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8910,7 +8910,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46213</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE144"/>
+  <dimension ref="A1:AE143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 46195-2022</t>
+          <t>A 4989-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44845</v>
+        <v>44593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -881,151 +881,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 46195-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44845</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Brandticka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 4989-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53784-2021</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44469</v>
+        <v>45751</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>44472</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44845</v>
+        <v>44592</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45302</v>
+        <v>45369</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45478</v>
+        <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45477</v>
+        <v>45733</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45756</v>
+        <v>45733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45235</v>
+        <v>44939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44868</v>
+        <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45602</v>
+        <v>45029</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46034</v>
+        <v>45259</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,8 +2577,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2621,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2635,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44875</v>
+        <v>45259</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2656,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2709,14 +2714,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44939</v>
+        <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2734,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44636</v>
+        <v>45583</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2802,7 +2807,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46043</v>
+        <v>45356</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45826</v>
+        <v>45701</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2991,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3005,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45259</v>
+        <v>44868</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,13 +3025,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45608</v>
+        <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45314</v>
+        <v>45003</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,13 +3171,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3229,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45161</v>
+        <v>45078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3298,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45981</v>
+        <v>45107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3318,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45701</v>
+        <v>45259</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45219</v>
+        <v>45231</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3473,13 +3468,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3522,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3536,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46098</v>
+        <v>45565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3552,7 +3542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3595,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3609,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44746</v>
+        <v>44945</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3625,7 +3615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3668,7 +3658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3682,10 +3672,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45078</v>
+        <v>44882</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3697,8 +3687,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3741,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45583</v>
+        <v>45062</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3814,7 +3809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45751</v>
+        <v>45702</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3843,8 +3838,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46127</v>
+        <v>45702</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3918,11 +3918,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45751</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3994,8 +3994,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4038,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4052,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45259</v>
+        <v>44882</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4073,7 +4078,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4121,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4135,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45733</v>
+        <v>45145</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4146,7 +4151,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4194,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4208,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45733</v>
+        <v>45610</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4219,7 +4224,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4267,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4281,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45161</v>
+        <v>45302</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4292,7 +4297,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4352,7 +4357,7 @@
         <v>45356</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45930</v>
+        <v>44746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4438,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4481,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45062</v>
+        <v>45314</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4510,8 +4515,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4571,7 +4581,7 @@
         <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4642,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4642,14 +4652,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45610</v>
+        <v>45394</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4672,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4715,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4729,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45565</v>
+        <v>44992</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4734,8 +4744,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4793,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4807,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4808,7 +4823,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4866,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4880,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45817</v>
+        <v>45265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4880,8 +4895,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4944,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4958,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44981</v>
+        <v>45511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4954,7 +4974,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4997,7 +5017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5011,10 +5031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45702</v>
+        <v>45701</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5052,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5095,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5109,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5110,7 +5130,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5153,7 +5173,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5167,10 +5187,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45145</v>
+        <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5182,8 +5202,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5251,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5265,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45161</v>
+        <v>45666</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5281,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5324,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5309,14 +5334,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45003</v>
+        <v>45477</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5329,7 +5354,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5397,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5411,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45478</v>
+        <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5402,7 +5427,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5445,7 +5470,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5459,10 +5484,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46149</v>
+        <v>45478</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5475,7 +5500,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>16.7</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5518,7 +5543,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5532,10 +5557,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45219</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5547,13 +5572,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>10.2</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5596,7 +5616,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5610,10 +5630,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45219</v>
+        <v>44524</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5625,13 +5645,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5689,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5703,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45219</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5703,13 +5718,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5752,7 +5762,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5766,10 +5776,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45107</v>
+        <v>45302</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5782,7 +5792,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5835,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5839,10 +5849,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46167</v>
+        <v>45756</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5855,7 +5865,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5898,7 +5908,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5908,14 +5918,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5928,7 +5938,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5971,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5985,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46177</v>
+        <v>45235</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6000,13 +6010,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6049,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44882</v>
+        <v>45259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6084,7 +6089,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6127,7 +6132,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6141,10 +6146,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46178</v>
+        <v>44875</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6162,7 +6167,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6205,7 +6210,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44746</v>
+        <v>45106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6234,8 +6239,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6278,7 +6288,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6292,10 +6302,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45163</v>
+        <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6308,7 +6318,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6351,7 +6361,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6365,10 +6375,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46189</v>
+        <v>44977</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6381,7 +6391,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6424,7 +6434,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6438,10 +6448,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44923</v>
+        <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6453,8 +6463,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6497,7 +6512,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6511,10 +6526,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44923</v>
+        <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6527,7 +6542,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6570,7 +6585,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6584,10 +6599,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45106</v>
+        <v>44845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6599,13 +6614,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6648,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6662,10 +6672,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45259</v>
+        <v>45370</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6683,7 +6693,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6726,7 +6736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6740,10 +6750,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45370</v>
+        <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6755,13 +6765,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6804,7 +6809,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6818,10 +6823,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44882</v>
+        <v>44923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6833,13 +6838,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45565</v>
+        <v>45107</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6965,14 +6965,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44592</v>
+        <v>45219</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6984,8 +6984,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7028,7 +7033,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7042,10 +7047,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45302</v>
+        <v>45219</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7057,8 +7062,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7101,7 +7111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7115,10 +7125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44992</v>
+        <v>45826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7130,13 +7140,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7179,7 +7184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7193,10 +7198,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46260</v>
+        <v>45702</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7208,8 +7213,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7252,7 +7262,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7266,10 +7276,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45259</v>
+        <v>45544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7281,13 +7291,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7330,7 +7335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45397</v>
+        <v>44981</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7360,7 +7365,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7403,7 +7408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7417,10 +7422,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46268</v>
+        <v>45608</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7432,13 +7437,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45702</v>
+        <v>45602</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7510,13 +7510,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7559,7 +7554,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7569,14 +7564,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44524</v>
+        <v>45981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7589,7 +7584,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7632,7 +7627,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7646,10 +7641,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45231</v>
+        <v>46034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7662,7 +7657,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45078</v>
+        <v>46043</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45356</v>
+        <v>46098</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45369</v>
+        <v>46127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7880,8 +7875,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45107</v>
+        <v>45565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45373</v>
+        <v>45817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8070,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45702</v>
+        <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8099,13 +8099,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>46149</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45544</v>
+        <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8251,7 +8246,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45029</v>
+        <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,8 +8318,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45701</v>
+        <v>46177</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,8 +8396,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46247</v>
+        <v>46189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8470,7 +8475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45265</v>
+        <v>46260</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8542,13 +8547,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45511</v>
+        <v>46268</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8620,8 +8620,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8681,7 +8686,7 @@
         <v>46246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8742,7 +8747,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8761,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44879</v>
+        <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,13 +8776,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,24 +8820,24 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45666</v>
+        <v>44637</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8903,14 +8903,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44637</v>
+        <v>45434</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8922,8 +8922,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8966,7 +8971,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8980,10 +8985,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45434</v>
+        <v>44918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8995,13 +9000,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9044,7 +9044,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9058,10 +9058,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44918</v>
+        <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10.7</v>
+        <v>44.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9131,10 +9131,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44830</v>
+        <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>44.5</v>
+        <v>17.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44543</v>
+        <v>44988</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9263,7 +9263,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44988</v>
+        <v>45565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9346,14 +9346,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45565</v>
+        <v>45348</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45348</v>
+        <v>44858</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>15.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44858</v>
+        <v>45608</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>15.8</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45608</v>
+        <v>45434</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9584,8 +9584,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9628,7 +9633,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9642,10 +9647,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45434</v>
+        <v>44988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9657,13 +9662,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9706,7 +9706,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44988</v>
+        <v>45582</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9779,7 +9779,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45582</v>
+        <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.8</v>
+        <v>40.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9866,10 +9866,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44936</v>
+        <v>45607</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>40.1</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9925,7 +9925,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9939,10 +9939,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45607</v>
+        <v>44936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4</v>
+        <v>55.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44936</v>
+        <v>45393</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>55.2</v>
+        <v>13.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45393</v>
+        <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10144,7 +10144,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45002</v>
+        <v>45608</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>12.7</v>
+        <v>11.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10217,7 +10217,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45608</v>
+        <v>45709</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>11.6</v>
+        <v>31.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10290,7 +10290,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10304,10 +10304,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45709</v>
+        <v>45901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>31.1</v>
+        <v>15.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45901</v>
+        <v>46030</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>15.1</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>46043</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10465,8 +10465,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10509,7 +10514,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10523,10 +10528,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10544,7 +10549,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>20</v>
+        <v>21.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10587,7 +10592,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10604,7 +10609,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10622,7 +10627,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10665,7 +10670,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10682,7 +10687,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10700,7 +10705,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>19.8</v>
+        <v>5.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10743,7 +10748,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10760,7 +10765,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10778,7 +10783,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10821,7 +10826,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10835,10 +10840,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10850,13 +10855,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>8.199999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46058</v>
+        <v>46136</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>27.6</v>
+        <v>8.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46136</v>
+        <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11001,8 +11001,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11045,7 +11050,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11062,7 +11067,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11080,7 +11085,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>11.1</v>
+        <v>17.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11123,7 +11128,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11140,7 +11145,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11158,7 +11163,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>17.7</v>
+        <v>28.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11201,7 +11206,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11218,7 +11223,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11236,7 +11241,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>28.1</v>
+        <v>15.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11279,7 +11284,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S 2015-2026</t>
+          <t>S 2017-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11296,7 +11301,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11314,7 +11319,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11354,10 +11359,10 @@
       </c>
       <c r="V142" s="2" t="inlineStr"/>
     </row>
-    <row r="143" ht="15" customHeight="1">
+    <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S 2017-2026</t>
+          <t>S 2047-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11371,10 +11376,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11392,7 +11397,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11431,84 +11436,6 @@
         <v>0</v>
       </c>
       <c r="V143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>S 2047-2026</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D144" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I144" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE143"/>
+  <dimension ref="A1:AE144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 4989-2022</t>
+          <t>A 46195-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44593</v>
+        <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -881,151 +881,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 4989-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 46195-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44845</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 54305-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45751</v>
+        <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44472</v>
+        <v>44845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44592</v>
+        <v>45302</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45369</v>
+        <v>45478</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45163</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45733</v>
+        <v>46034</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45733</v>
+        <v>46043</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44939</v>
+        <v>45235</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44746</v>
+        <v>44868</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45029</v>
+        <v>45756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45259</v>
+        <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2575,11 +2575,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2626,7 +2621,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2635,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45259</v>
+        <v>44875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2656,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2714,14 +2709,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45161</v>
+        <v>44939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2734,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45583</v>
+        <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45356</v>
+        <v>45608</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45701</v>
+        <v>46098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2948,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2991,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44868</v>
+        <v>45259</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,8 +3020,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45478</v>
+        <v>45314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3098,8 +3098,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3152,14 +3157,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45003</v>
+        <v>46127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,8 +3176,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3225,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3225,14 +3235,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45078</v>
+        <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3255,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3298,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3312,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45107</v>
+        <v>45161</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3318,7 +3328,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3361,7 +3371,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3385,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45259</v>
+        <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3390,13 +3400,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45231</v>
+        <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3468,8 +3473,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3522,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3536,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45565</v>
+        <v>45219</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3541,8 +3551,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3600,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3614,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44945</v>
+        <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3615,7 +3630,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3658,7 +3673,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3672,10 +3687,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44882</v>
+        <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,13 +3702,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3746,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3760,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45062</v>
+        <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3766,7 +3776,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3809,7 +3819,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3823,10 +3833,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45702</v>
+        <v>44746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3838,13 +3848,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3892,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45702</v>
+        <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3916,13 +3921,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45583</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3994,13 +3994,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4038,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44882</v>
+        <v>45751</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4070,11 +4065,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4121,7 +4111,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4135,10 +4125,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45145</v>
+        <v>46149</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4151,7 +4141,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>16.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4194,7 +4184,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45610</v>
+        <v>45751</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4267,7 +4257,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45302</v>
+        <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4296,8 +4286,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45356</v>
+        <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4370,7 +4365,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44746</v>
+        <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4438,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45314</v>
+        <v>45161</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4515,13 +4510,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4564,7 +4554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4578,10 +4568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44992</v>
+        <v>45356</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4593,13 +4583,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4642,7 +4627,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4652,14 +4637,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45394</v>
+        <v>45062</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4672,7 +4657,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4715,7 +4700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4729,10 +4714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44992</v>
+        <v>46167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4744,13 +4729,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4793,7 +4773,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4807,10 +4787,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45078</v>
+        <v>44992</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4822,8 +4802,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4866,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4880,10 +4865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45265</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4895,13 +4880,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4944,7 +4924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4958,10 +4938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45511</v>
+        <v>44945</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4974,7 +4954,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5017,7 +4997,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5031,10 +5011,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45701</v>
+        <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5046,13 +5026,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5095,7 +5070,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5109,10 +5084,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45219</v>
+        <v>45702</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5130,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5173,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5187,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44879</v>
+        <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5208,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5251,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5265,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45666</v>
+        <v>45145</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5281,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5324,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5338,10 +5313,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45477</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5354,7 +5329,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5397,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5411,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>46177</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5426,8 +5401,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5470,7 +5450,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5480,14 +5460,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45478</v>
+        <v>45003</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5500,7 +5480,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5543,7 +5523,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5557,10 +5537,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>46178</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5572,8 +5552,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5616,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5630,10 +5615,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44524</v>
+        <v>45478</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5646,7 +5631,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5689,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5703,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>45219</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5718,8 +5703,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5762,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5776,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45302</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5791,8 +5781,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5835,7 +5830,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5849,10 +5844,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45756</v>
+        <v>46189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5865,7 +5860,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5908,7 +5903,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5922,10 +5917,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45397</v>
+        <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5937,8 +5932,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45235</v>
+        <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6064,14 +6064,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45259</v>
+        <v>45394</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6083,13 +6083,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6132,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6146,10 +6141,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44875</v>
+        <v>46260</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,13 +6156,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6210,7 +6200,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6224,10 +6214,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45106</v>
+        <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6245,7 +6235,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6288,7 +6278,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6302,10 +6292,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45751</v>
+        <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6361,7 +6351,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6375,10 +6365,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44977</v>
+        <v>45163</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6391,7 +6381,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6434,7 +6424,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6448,10 +6438,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45219</v>
+        <v>44923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6463,13 +6453,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6512,7 +6497,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6526,10 +6511,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44636</v>
+        <v>44923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6542,7 +6527,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6585,7 +6570,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6599,10 +6584,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44845</v>
+        <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6614,8 +6599,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6658,7 +6648,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6672,10 +6662,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45370</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6693,7 +6683,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6736,7 +6726,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6750,10 +6740,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44923</v>
+        <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6765,8 +6755,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6809,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6823,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44923</v>
+        <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6838,8 +6833,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45107</v>
+        <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6911,8 +6911,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6955,7 +6960,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6969,10 +6974,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45219</v>
+        <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6984,13 +6989,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7043,14 +7043,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45219</v>
+        <v>44592</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7062,13 +7062,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7111,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7125,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45826</v>
+        <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7141,7 +7136,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7184,7 +7179,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7198,10 +7193,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45702</v>
+        <v>44992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7219,7 +7214,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7262,7 +7257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7276,10 +7271,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45544</v>
+        <v>45259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7291,8 +7286,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44981</v>
+        <v>45397</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45608</v>
+        <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45602</v>
+        <v>46246</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7510,8 +7510,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7554,7 +7559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7564,14 +7569,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45981</v>
+        <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7583,8 +7588,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7627,7 +7637,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7641,10 +7651,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46034</v>
+        <v>44524</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7657,7 +7667,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7700,7 +7710,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7714,10 +7724,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46043</v>
+        <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7730,7 +7740,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7783,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7797,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46098</v>
+        <v>45078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7803,7 +7813,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7846,7 +7856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46127</v>
+        <v>46276</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7875,13 +7885,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45565</v>
+        <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7954,7 +7959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7997,7 +8002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45817</v>
+        <v>45369</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8027,7 +8032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8084,10 +8089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45930</v>
+        <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46149</v>
+        <v>45373</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8173,7 +8178,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>16.7</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46167</v>
+        <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8245,8 +8250,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8289,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8303,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46178</v>
+        <v>44977</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8318,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46177</v>
+        <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,13 +8401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46189</v>
+        <v>45029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46260</v>
+        <v>45701</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46268</v>
+        <v>45265</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46246</v>
+        <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8698,13 +8698,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8747,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8761,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46247</v>
+        <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8776,8 +8771,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,24 +8820,24 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44637</v>
+        <v>45666</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8903,14 +8903,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45434</v>
+        <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8922,13 +8922,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8971,7 +8966,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8985,10 +8980,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44918</v>
+        <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9000,8 +8995,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9044,7 +9044,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9058,10 +9058,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44830</v>
+        <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>44.5</v>
+        <v>10.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9131,10 +9131,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44543</v>
+        <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>17.5</v>
+        <v>44.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9190,7 +9190,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44988</v>
+        <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9263,7 +9263,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45565</v>
+        <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9346,14 +9346,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45348</v>
+        <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44858</v>
+        <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>15.8</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45608</v>
+        <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>15.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45434</v>
+        <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9584,13 +9584,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9633,7 +9628,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9647,10 +9642,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44988</v>
+        <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9662,8 +9657,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9706,7 +9706,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45582</v>
+        <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>13.8</v>
+        <v>7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9779,7 +9779,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44936</v>
+        <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>40.1</v>
+        <v>13.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9866,10 +9866,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45607</v>
+        <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>40.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9925,7 +9925,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9939,10 +9939,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44936</v>
+        <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>55.2</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45393</v>
+        <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>13.1</v>
+        <v>55.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45002</v>
+        <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10144,7 +10144,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45608</v>
+        <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10217,7 +10217,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45709</v>
+        <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>31.1</v>
+        <v>11.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10290,7 +10290,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10304,10 +10304,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45901</v>
+        <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>15.1</v>
+        <v>31.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46030</v>
+        <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>15.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46043</v>
+        <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10465,13 +10465,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10514,7 +10509,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10528,10 +10523,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10549,7 +10544,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>21.6</v>
+        <v>20</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10592,7 +10587,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10609,7 +10604,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10627,7 +10622,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10670,7 +10665,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10687,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10705,7 +10700,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.4</v>
+        <v>19.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10748,7 +10743,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10765,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10783,7 +10778,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10826,7 +10821,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10840,10 +10835,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10855,8 +10850,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>27.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46136</v>
+        <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.1</v>
+        <v>27.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46210</v>
+        <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11001,13 +11001,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>11.1</v>
+        <v>8.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11050,7 +11045,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11067,7 +11062,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11085,7 +11080,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>17.7</v>
+        <v>11.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11128,7 +11123,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11145,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11163,7 +11158,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>28.1</v>
+        <v>17.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11206,7 +11201,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 2015-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11223,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11241,7 +11236,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11284,7 +11279,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S 2017-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11301,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11319,123 +11314,201 @@
         </is>
       </c>
       <c r="I142" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>S 2017-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E143" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>S 2047-2026</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D143" s="1" t="n">
+      <c r="D144" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="E143" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
+      <c r="E144" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I143" t="n">
+      <c r="I144" t="n">
         <v>18.5</v>
       </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="2" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44845</v>
+        <v>45751</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45478</v>
+        <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46034</v>
+        <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46043</v>
+        <v>45231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45235</v>
+        <v>45565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44868</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45756</v>
+        <v>45314</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2504,8 +2504,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2548,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2562,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45602</v>
+        <v>45302</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2578,7 +2583,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2621,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2635,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44875</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2650,13 +2655,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44939</v>
+        <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44636</v>
+        <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45608</v>
+        <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46098</v>
+        <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,8 +2947,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2991,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3005,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45259</v>
+        <v>45602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3018,11 +3023,6 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3069,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45314</v>
+        <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3098,13 +3098,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46127</v>
+        <v>45756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3176,13 +3171,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3225,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3235,14 +3225,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45981</v>
+        <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3255,7 +3245,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3298,7 +3288,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3312,10 +3302,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45161</v>
+        <v>44923</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3328,7 +3318,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3371,7 +3361,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45930</v>
+        <v>45544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3391,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3434,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3448,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45701</v>
+        <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3473,13 +3463,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3522,7 +3507,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3536,10 +3521,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45219</v>
+        <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3551,13 +3536,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3600,7 +3580,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3614,10 +3594,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45565</v>
+        <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3630,7 +3610,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3673,7 +3653,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3683,14 +3663,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45817</v>
+        <v>44939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3703,7 +3683,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3746,7 +3726,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3760,10 +3740,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45826</v>
+        <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3775,8 +3755,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3819,7 +3804,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3833,10 +3818,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44746</v>
+        <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3848,8 +3833,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3892,7 +3882,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3906,10 +3896,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45078</v>
+        <v>46098</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3922,7 +3912,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3982,7 +3972,7 @@
         <v>45583</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4038,7 +4028,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4052,10 +4042,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45751</v>
+        <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4068,7 +4058,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4111,7 +4101,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4125,10 +4115,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46149</v>
+        <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4141,7 +4131,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>16.7</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,7 +4174,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4198,10 +4188,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45751</v>
+        <v>45107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4214,7 +4204,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4257,7 +4247,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4267,14 +4257,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45259</v>
+        <v>45981</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4286,13 +4276,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4320,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,10 +4334,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45733</v>
+        <v>45259</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4364,8 +4349,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4408,7 +4398,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,10 +4412,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45733</v>
+        <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4438,7 +4428,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4481,7 +4471,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 55416-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4495,10 +4485,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45161</v>
+        <v>44882</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4510,8 +4500,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4554,7 +4549,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4568,10 +4563,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45356</v>
+        <v>46127</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4583,8 +4578,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45062</v>
+        <v>45702</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4656,8 +4656,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4700,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46167</v>
+        <v>44882</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4729,8 +4734,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4773,7 +4783,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4787,10 +4797,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44992</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4802,13 +4812,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45356</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4881,7 +4886,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44945</v>
+        <v>45078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4954,7 +4959,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4997,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5011,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>45565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5027,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5070,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5084,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45702</v>
+        <v>45826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5099,13 +5104,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45702</v>
+        <v>45701</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45145</v>
+        <v>45817</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>45930</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46177</v>
+        <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5401,13 +5401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5450,7 +5445,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5460,14 +5455,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45003</v>
+        <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5480,7 +5475,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5523,7 +5518,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5537,10 +5532,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46178</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5552,13 +5547,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5591,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45478</v>
+        <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,8 +5620,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5669,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5688,10 +5683,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45219</v>
+        <v>44977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5703,13 +5698,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5752,7 +5742,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5769,7 +5759,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5787,7 +5777,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5830,7 +5820,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5844,10 +5834,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46189</v>
+        <v>46149</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5860,7 +5850,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.7</v>
+        <v>16.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5903,7 +5893,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5917,10 +5907,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45219</v>
+        <v>46167</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5932,13 +5922,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5966,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5980,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45107</v>
+        <v>45702</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6010,8 +5995,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6044,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6064,14 +6054,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45394</v>
+        <v>44981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6084,7 +6074,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6127,7 +6117,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6141,10 +6131,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46260</v>
+        <v>46177</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6156,8 +6146,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6200,7 +6195,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6210,14 +6205,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44882</v>
+        <v>44592</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6229,13 +6224,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6278,7 +6268,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6292,10 +6282,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44746</v>
+        <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6308,7 +6298,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6351,7 +6341,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6365,10 +6355,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45163</v>
+        <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6381,7 +6371,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6424,7 +6414,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6438,10 +6428,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44923</v>
+        <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6454,7 +6444,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6497,7 +6487,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6511,10 +6501,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44923</v>
+        <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6527,7 +6517,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6570,7 +6560,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6580,14 +6570,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45106</v>
+        <v>45003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6599,13 +6589,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6648,7 +6633,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6662,10 +6647,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6677,13 +6662,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6726,7 +6706,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6740,10 +6720,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45259</v>
+        <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6755,13 +6735,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6804,7 +6779,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6818,10 +6793,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45370</v>
+        <v>45302</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6833,13 +6808,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6852,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6866,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44882</v>
+        <v>46260</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6911,13 +6881,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6960,7 +6925,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6974,10 +6939,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45565</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6989,8 +6954,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7033,7 +7003,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7043,14 +7013,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44592</v>
+        <v>46268</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7062,8 +7032,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7081,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7095,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45302</v>
+        <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7135,8 +7110,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7179,7 +7159,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7193,10 +7173,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44992</v>
+        <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7208,13 +7188,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7257,7 +7232,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7271,10 +7246,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45259</v>
+        <v>45235</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7286,13 +7261,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7305,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7319,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45397</v>
+        <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7364,8 +7334,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7408,7 +7383,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7422,10 +7397,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46247</v>
+        <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7438,7 +7413,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7498,7 +7473,7 @@
         <v>46246</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7559,7 +7534,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7573,10 +7548,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45702</v>
+        <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7588,13 +7563,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7637,7 +7607,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7651,10 +7621,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44524</v>
+        <v>45370</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7666,8 +7636,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7710,7 +7685,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7724,10 +7699,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45231</v>
+        <v>44923</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7740,7 +7715,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7783,7 +7758,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7797,10 +7772,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45078</v>
+        <v>46247</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7813,7 +7788,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7856,7 +7831,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7870,10 +7845,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46276</v>
+        <v>45107</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7886,7 +7861,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7929,7 +7904,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7943,10 +7918,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7958,8 +7933,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7982,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +7996,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45369</v>
+        <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8031,8 +8011,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8060,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8074,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45107</v>
+        <v>46178</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8104,8 +8089,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45373</v>
+        <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8168,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45702</v>
+        <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8250,13 +8240,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8284,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8298,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44977</v>
+        <v>45702</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8328,8 +8313,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8362,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8376,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45544</v>
+        <v>45702</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8401,8 +8391,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45029</v>
+        <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8475,7 +8470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8513,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8532,10 +8527,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45701</v>
+        <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8547,8 +8542,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45265</v>
+        <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8620,13 +8620,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8664,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8678,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45511</v>
+        <v>45265</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8698,8 +8693,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44879</v>
+        <v>45511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,13 +8771,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45666</v>
+        <v>44879</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8847,6 +8842,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -8910,7 +8910,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46213</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45751</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44746</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45314</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45302</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44923</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>46098</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45583</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45981</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45259</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44882</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>46127</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45702</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44882</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45356</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45701</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45817</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45930</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46149</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46167</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45702</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46177</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44592</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45302</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46260</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>46268</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45235</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>46246</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45370</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44923</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>46247</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45107</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46178</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45702</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45702</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45265</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>44879</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46213</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45751</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>44746</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45314</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45302</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45397</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45259</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44923</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45259</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>46098</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45583</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>45981</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45259</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44882</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>46127</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45702</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44882</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45356</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45701</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45817</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45930</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>44977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46149</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46167</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45702</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46177</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44592</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45302</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46260</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>46268</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45235</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>46246</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45370</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44923</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>46247</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45107</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46178</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45702</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45702</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45265</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>44879</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45434</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45348</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45434</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44988</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44936</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45393</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45608</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46044</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46058</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46136</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46210</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46213</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE144"/>
+  <dimension ref="A1:AE141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54411-2021</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44473</v>
+        <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44739</v>
+        <v>44845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54305-2021</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44472</v>
+        <v>45302</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45751</v>
+        <v>45235</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44746</v>
+        <v>44868</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45029</v>
+        <v>44875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,8 +2066,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2115,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45701</v>
+        <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2145,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2188,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2193,14 +2198,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45078</v>
+        <v>44939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2218,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2261,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45231</v>
+        <v>44636</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2291,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45565</v>
+        <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2364,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45666</v>
+        <v>45602</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2432,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2475,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2515,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2553,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2567,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45302</v>
+        <v>45314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2582,8 +2587,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2626,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2656,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45397</v>
+        <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2772,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2786,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45478</v>
+        <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,8 +2811,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2845,7 +2860,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2859,10 +2874,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46034</v>
+        <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2875,7 +2890,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2918,7 +2933,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2932,10 +2947,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45259</v>
+        <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2968,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3011,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3025,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45602</v>
+        <v>44746</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3041,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3084,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3079,14 +3094,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46043</v>
+        <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3114,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3157,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3156,10 +3171,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45756</v>
+        <v>46127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,8 +3186,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3235,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3229,10 +3249,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44636</v>
+        <v>45078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3245,7 +3265,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3288,7 +3308,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3302,10 +3322,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44923</v>
+        <v>45583</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3318,7 +3338,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3361,7 +3381,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3375,10 +3395,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45544</v>
+        <v>45751</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3391,7 +3411,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3434,7 +3454,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3448,10 +3468,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45608</v>
+        <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3464,7 +3484,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3507,7 +3527,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3521,10 +3541,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45733</v>
+        <v>45259</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3536,8 +3556,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3580,7 +3605,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3594,10 +3619,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45733</v>
+        <v>45930</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3610,7 +3635,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3653,7 +3678,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3663,14 +3688,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44939</v>
+        <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3683,7 +3708,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3726,7 +3751,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3740,10 +3765,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45259</v>
+        <v>45733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3755,13 +3780,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3804,7 +3824,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3818,10 +3838,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45259</v>
+        <v>45161</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3833,13 +3853,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3882,7 +3897,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3896,10 +3911,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46098</v>
+        <v>45356</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3912,7 +3927,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3970,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3969,10 +3984,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45583</v>
+        <v>46034</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3985,7 +4000,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4028,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4042,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44868</v>
+        <v>45062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4058,7 +4073,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4101,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4115,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45478</v>
+        <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4131,7 +4146,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4174,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4188,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45107</v>
+        <v>45817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4204,7 +4219,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4247,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4257,14 +4272,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45981</v>
+        <v>44992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4276,8 +4291,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4320,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4334,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45259</v>
+        <v>45610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4349,13 +4369,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4415,7 +4430,7 @@
         <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4471,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55416-2022</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4485,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44882</v>
+        <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4500,13 +4515,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4549,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4563,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46127</v>
+        <v>45702</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4580,11 +4590,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4627,7 +4637,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4644,7 +4654,7 @@
         <v>45702</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4672,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4715,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4729,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44882</v>
+        <v>45145</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4734,13 +4744,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4813,7 +4818,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4861,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4866,14 +4871,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45356</v>
+        <v>45003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4886,7 +4891,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4934,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45078</v>
+        <v>46149</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4964,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>16.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45565</v>
+        <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5037,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5080,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5094,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45826</v>
+        <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5104,8 +5109,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>10.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5158,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5172,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45701</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5193,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45817</v>
+        <v>46167</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5266,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45930</v>
+        <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5328,8 +5338,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5387,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5401,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>45107</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5402,7 +5417,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5445,7 +5460,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5459,10 +5474,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44524</v>
+        <v>46177</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5474,8 +5489,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5518,7 +5538,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5528,14 +5548,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45394</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5548,7 +5568,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5591,7 +5611,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5605,10 +5625,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5620,13 +5640,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5669,7 +5684,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5683,10 +5698,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44977</v>
+        <v>44882</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5696,6 +5711,11 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -5742,7 +5762,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5756,10 +5776,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>44746</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5771,13 +5791,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5820,7 +5835,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5834,10 +5849,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46149</v>
+        <v>45163</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5850,7 +5865,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>16.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5908,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5907,10 +5922,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46167</v>
+        <v>44923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5923,7 +5938,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5966,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5980,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45702</v>
+        <v>44923</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5995,13 +6010,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6044,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6058,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44981</v>
+        <v>45106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6073,8 +6083,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6117,7 +6132,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6131,10 +6146,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46177</v>
+        <v>45259</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6152,7 +6167,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6195,7 +6210,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6205,14 +6220,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44592</v>
+        <v>45370</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6224,8 +6239,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6268,7 +6288,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6282,10 +6302,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45369</v>
+        <v>46260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6298,7 +6318,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6341,7 +6361,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6355,10 +6375,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46189</v>
+        <v>45565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6371,7 +6391,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6414,7 +6434,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6424,14 +6444,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45161</v>
+        <v>44592</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6444,7 +6464,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6487,7 +6507,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6501,10 +6521,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45356</v>
+        <v>45302</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6517,7 +6537,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6560,7 +6580,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6570,14 +6590,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45003</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6589,8 +6609,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6633,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6647,10 +6672,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45062</v>
+        <v>46268</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6662,8 +6687,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6706,7 +6736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6720,10 +6750,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45145</v>
+        <v>45259</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6735,8 +6765,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6779,7 +6814,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6793,10 +6828,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45302</v>
+        <v>45397</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6809,7 +6844,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6852,7 +6887,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6866,10 +6901,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46260</v>
+        <v>45702</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6881,8 +6916,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6925,7 +6965,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6939,10 +6979,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44992</v>
+        <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6954,13 +6994,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7003,7 +7038,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7017,10 +7052,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46268</v>
+        <v>45231</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7032,13 +7067,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7081,7 +7111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7095,10 +7125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45219</v>
+        <v>45078</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7110,13 +7140,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7159,7 +7184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7173,10 +7198,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45161</v>
+        <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7189,7 +7214,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7232,7 +7257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7246,10 +7271,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45235</v>
+        <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7262,7 +7287,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7305,7 +7330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7319,10 +7344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45106</v>
+        <v>45107</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7334,13 +7359,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7383,7 +7403,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7397,10 +7417,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45751</v>
+        <v>45373</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7413,7 +7433,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7456,7 +7476,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7470,10 +7490,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7491,7 +7511,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7534,7 +7554,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7548,10 +7568,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44845</v>
+        <v>46247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7564,7 +7584,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7607,7 +7627,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7621,10 +7641,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45370</v>
+        <v>44977</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7636,13 +7656,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7685,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7699,10 +7714,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44923</v>
+        <v>45544</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7715,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7758,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7772,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7787,8 +7802,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7831,7 +7851,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7845,10 +7865,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45107</v>
+        <v>45029</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7861,7 +7881,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7904,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7918,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45219</v>
+        <v>45701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7933,13 +7953,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7982,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7996,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45219</v>
+        <v>45265</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8017,7 +8032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8060,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8074,10 +8089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46178</v>
+        <v>45511</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8089,13 +8104,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8138,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8152,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45163</v>
+        <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8167,8 +8177,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8228,7 +8243,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8284,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8298,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45702</v>
+        <v>45666</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8313,13 +8328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8362,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8376,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45702</v>
+        <v>45478</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8391,13 +8401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44746</v>
+        <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8470,7 +8475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44992</v>
+        <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8548,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8601,14 +8606,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45394</v>
+        <v>45756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,24 +8669,24 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45265</v>
+        <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8693,13 +8698,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,24 +8742,24 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45511</v>
+        <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,8 +8771,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,24 +8820,24 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44879</v>
+        <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8844,13 +8849,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>10.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8903,14 +8903,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44637</v>
+        <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>44.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45434</v>
+        <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8995,13 +8995,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9044,7 +9039,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9058,10 +9053,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44918</v>
+        <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9074,7 +9069,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9117,7 +9112,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9127,14 +9122,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44830</v>
+        <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9147,7 +9142,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>44.5</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9190,7 +9185,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9204,10 +9199,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44543</v>
+        <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9220,7 +9215,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9263,7 +9258,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9277,10 +9272,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44988</v>
+        <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9293,7 +9288,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>9.4</v>
+        <v>15.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9336,7 +9331,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9346,14 +9341,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45565</v>
+        <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9366,7 +9361,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9409,7 +9404,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9423,10 +9418,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45348</v>
+        <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9438,8 +9433,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44858</v>
+        <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>15.8</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45608</v>
+        <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>13.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45434</v>
+        <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9657,13 +9657,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>9.800000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9706,7 +9701,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9720,10 +9715,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44988</v>
+        <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9736,7 +9731,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9779,7 +9774,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9793,10 +9788,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45582</v>
+        <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9809,7 +9804,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.8</v>
+        <v>55.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9852,7 +9847,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9866,10 +9861,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44936</v>
+        <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9882,7 +9877,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>40.1</v>
+        <v>13.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9925,7 +9920,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9939,10 +9934,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45607</v>
+        <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9955,7 +9950,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4</v>
+        <v>12.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9998,7 +9993,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10012,10 +10007,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44936</v>
+        <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10028,7 +10023,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>55.2</v>
+        <v>11.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10071,7 +10066,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10085,10 +10080,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45393</v>
+        <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10101,7 +10096,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>13.1</v>
+        <v>31.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10144,7 +10139,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10158,10 +10153,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45002</v>
+        <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10174,7 +10169,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>12.7</v>
+        <v>15.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10217,7 +10212,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,10 +10226,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45608</v>
+        <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10247,7 +10242,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10290,7 +10285,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10304,10 +10299,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45709</v>
+        <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10319,8 +10314,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>31.1</v>
+        <v>20</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10377,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45901</v>
+        <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10392,8 +10392,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>15.1</v>
+        <v>21.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10436,7 +10441,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10450,10 +10455,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10465,8 +10470,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>5.3</v>
+        <v>19.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10509,7 +10519,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10523,10 +10533,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10544,7 +10554,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10587,7 +10597,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10604,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10622,7 +10632,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>21.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10665,7 +10675,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10679,10 +10689,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10694,13 +10704,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>19.8</v>
+        <v>27.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10743,7 +10748,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10757,10 +10762,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46044</v>
+        <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10772,13 +10777,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46044</v>
+        <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.199999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46058</v>
+        <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10928,8 +10928,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>27.6</v>
+        <v>17.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10972,7 +10977,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10986,10 +10991,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46136</v>
+        <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11001,8 +11006,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>8.1</v>
+        <v>28.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11045,7 +11055,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11062,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11080,7 +11090,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>11.1</v>
+        <v>15.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11123,7 +11133,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2017-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11140,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11158,7 +11168,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>17.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11198,10 +11208,10 @@
       </c>
       <c r="V140" s="2" t="inlineStr"/>
     </row>
-    <row r="141" ht="15" customHeight="1">
+    <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2047-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11215,10 +11225,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11236,7 +11246,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>28.1</v>
+        <v>18.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11275,240 +11285,6 @@
         <v>0</v>
       </c>
       <c r="V141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>S 2015-2026</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D142" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E142" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I142" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>S 2017-2026</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E143" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I143" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>S 2047-2026</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D144" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I144" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44845</v>
+        <v>45751</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45235</v>
+        <v>45701</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44868</v>
+        <v>45029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44875</v>
+        <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,13 +2066,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2115,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46043</v>
+        <v>45231</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2145,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2188,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2198,14 +2193,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44939</v>
+        <v>45565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2218,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2261,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44636</v>
+        <v>45314</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,8 +2285,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45826</v>
+        <v>45302</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45602</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2497,7 +2497,7 @@
         <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45314</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2587,13 +2587,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45608</v>
+        <v>44923</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45161</v>
+        <v>46034</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2734,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45701</v>
+        <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2811,13 +2806,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2860,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2874,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46098</v>
+        <v>45544</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2890,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2933,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2947,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45219</v>
+        <v>45602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2962,13 +2952,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3011,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3025,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44746</v>
+        <v>45733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3041,7 +3026,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3084,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3094,14 +3079,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45981</v>
+        <v>45733</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3114,7 +3099,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3157,7 +3142,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3167,14 +3152,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46127</v>
+        <v>44939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3186,13 +3171,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3235,7 +3215,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3249,10 +3229,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45078</v>
+        <v>45259</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3262,6 +3242,11 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3308,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3322,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45583</v>
+        <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3337,8 +3322,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3381,7 +3371,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3395,10 +3385,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45751</v>
+        <v>45583</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3411,7 +3401,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3454,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3468,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3484,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3527,7 +3517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3541,10 +3531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45259</v>
+        <v>46098</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3556,13 +3546,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3605,7 +3590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3619,10 +3604,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45930</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3635,7 +3620,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3678,7 +3663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3692,10 +3677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45733</v>
+        <v>45107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3708,7 +3693,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3751,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3765,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45733</v>
+        <v>45608</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3781,7 +3766,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3824,7 +3809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3838,10 +3823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45161</v>
+        <v>45826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3854,7 +3839,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3897,7 +3882,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3911,10 +3896,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45356</v>
+        <v>45259</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3926,8 +3911,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3970,7 +3960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3984,10 +3974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46034</v>
+        <v>44945</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4000,7 +3990,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45062</v>
+        <v>46127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4072,8 +4062,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4111,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45565</v>
+        <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4145,8 +4140,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45817</v>
+        <v>44882</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4218,8 +4218,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4267,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4281,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44992</v>
+        <v>45610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4291,13 +4296,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45610</v>
+        <v>45356</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4423,14 +4423,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44945</v>
+        <v>45981</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44981</v>
+        <v>45565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45702</v>
+        <v>45817</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4588,13 +4588,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4637,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4651,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45702</v>
+        <v>45930</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4666,13 +4661,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4715,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4729,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45145</v>
+        <v>46149</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4745,7 +4735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>16.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4788,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4802,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4818,7 +4808,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4861,7 +4851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4871,14 +4861,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45003</v>
+        <v>46167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4891,7 +4881,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4934,7 +4924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4948,10 +4938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46149</v>
+        <v>46177</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4963,8 +4953,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>16.7</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5007,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5021,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45478</v>
+        <v>45701</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5036,8 +5031,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5080,7 +5080,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45219</v>
+        <v>46189</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5109,13 +5109,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.2</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5187,13 +5182,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5250,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46167</v>
+        <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5266,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5323,10 +5313,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45219</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5338,13 +5328,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5387,7 +5372,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5401,10 +5386,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45107</v>
+        <v>44875</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5416,8 +5401,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5460,7 +5450,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5474,10 +5464,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46177</v>
+        <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5489,13 +5479,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5538,7 +5523,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5548,14 +5533,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45394</v>
+        <v>45219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5567,8 +5552,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5611,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5625,10 +5615,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46189</v>
+        <v>45702</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5640,8 +5630,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5684,7 +5679,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5698,10 +5693,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44882</v>
+        <v>46260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5713,13 +5708,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5762,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5776,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44746</v>
+        <v>44981</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5792,7 +5782,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5835,7 +5825,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5845,14 +5835,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45163</v>
+        <v>44592</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5865,7 +5855,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5908,7 +5898,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5922,10 +5912,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44923</v>
+        <v>45369</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5938,7 +5928,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5971,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5985,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44923</v>
+        <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6011,7 +6001,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6044,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6068,10 +6058,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45106</v>
+        <v>45356</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6083,13 +6073,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6132,7 +6117,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6146,10 +6131,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45259</v>
+        <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6167,7 +6152,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6210,7 +6195,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6220,14 +6205,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45370</v>
+        <v>45003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6237,11 +6222,6 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -6288,7 +6268,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6302,10 +6282,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46260</v>
+        <v>45062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6318,7 +6298,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6361,7 +6341,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6375,10 +6355,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45565</v>
+        <v>45145</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6391,7 +6371,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6434,7 +6414,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6444,14 +6424,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44592</v>
+        <v>45302</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6464,7 +6444,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6507,7 +6487,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6521,10 +6501,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45302</v>
+        <v>44992</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6536,8 +6516,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6580,7 +6565,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6594,10 +6579,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44992</v>
+        <v>46246</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6615,7 +6600,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6658,7 +6643,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6672,10 +6657,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46268</v>
+        <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6693,7 +6678,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6736,7 +6721,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6750,10 +6735,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45259</v>
+        <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6765,13 +6750,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6814,7 +6794,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6828,10 +6808,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45397</v>
+        <v>46247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6844,7 +6824,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6887,7 +6867,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6901,10 +6881,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45702</v>
+        <v>45235</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6916,13 +6896,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6965,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6979,10 +6954,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44524</v>
+        <v>45106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6994,8 +6969,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7038,7 +7018,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7052,10 +7032,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45231</v>
+        <v>45751</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7068,7 +7048,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7111,7 +7091,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7125,10 +7105,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45078</v>
+        <v>46178</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7140,8 +7120,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7184,7 +7169,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7198,10 +7183,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45356</v>
+        <v>44845</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7214,7 +7199,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7257,7 +7242,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7271,10 +7256,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7286,8 +7271,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7330,7 +7320,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7344,10 +7334,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45107</v>
+        <v>44923</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7360,7 +7350,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7403,7 +7393,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7417,10 +7407,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45373</v>
+        <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7433,7 +7423,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7476,7 +7466,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7490,10 +7480,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7511,7 +7501,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7554,7 +7544,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7568,10 +7558,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46247</v>
+        <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7583,8 +7573,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>9.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7627,7 +7622,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7641,10 +7636,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44977</v>
+        <v>46276</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7657,7 +7652,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7700,7 +7695,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7714,10 +7709,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45544</v>
+        <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7730,7 +7725,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7768,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7782,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46246</v>
+        <v>45702</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45029</v>
+        <v>45702</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7880,8 +7875,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45701</v>
+        <v>44746</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45265</v>
+        <v>44992</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8085,14 +8085,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45511</v>
+        <v>45394</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44879</v>
+        <v>45265</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46276</v>
+        <v>45511</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45666</v>
+        <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8326,6 +8326,11 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -8372,7 +8377,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8391,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45478</v>
+        <v>45666</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8402,7 +8407,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8462,7 +8467,7 @@
         <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8518,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46178</v>
+        <v>45478</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8547,13 +8552,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8613,7 +8613,7 @@
         <v>45756</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 46195-2022</t>
+          <t>A 4989-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44845</v>
+        <v>44593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -881,151 +881,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 46195-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44845</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Brandticka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 4989-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44739</v>
+        <v>45219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1701,8 +1701,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1745,7 +1750,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45751</v>
+        <v>44739</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1780,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1835,7 +1840,7 @@
         <v>44746</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1913,7 @@
         <v>45701</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1964,7 +1969,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1983,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45029</v>
+        <v>45265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1993,8 +1998,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2047,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45078</v>
+        <v>45511</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2077,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2120,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2134,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45231</v>
+        <v>44879</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2139,8 +2149,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2198,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2212,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45565</v>
+        <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2228,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2271,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2285,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45314</v>
+        <v>44845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2285,13 +2300,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2344,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2358,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45302</v>
+        <v>45583</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2364,7 +2374,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2417,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2431,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2437,7 +2447,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>45751</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,13 +2519,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2563,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2577,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>45302</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2593,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44923</v>
+        <v>45478</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46034</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2734,7 +2739,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2782,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2796,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46043</v>
+        <v>45751</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2812,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2855,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2869,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45544</v>
+        <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2879,8 +2884,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2933,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2947,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45602</v>
+        <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2963,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3006,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3013,7 +3023,7 @@
         <v>45733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3026,7 +3036,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3079,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3093,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45733</v>
+        <v>45756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3099,7 +3109,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3142,7 +3152,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3152,14 +3162,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44939</v>
+        <v>45161</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3172,7 +3182,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3215,7 +3225,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3229,10 +3239,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45259</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3244,13 +3254,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3298,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,10 +3312,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45259</v>
+        <v>45602</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3322,13 +3327,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45583</v>
+        <v>45062</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44868</v>
+        <v>45235</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46098</v>
+        <v>44992</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3546,8 +3546,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3590,7 +3595,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3604,10 +3609,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>44868</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3620,7 +3625,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3663,7 +3668,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3677,10 +3682,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45107</v>
+        <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3693,7 +3698,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3741,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45608</v>
+        <v>44945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3766,7 +3771,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3809,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3823,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45826</v>
+        <v>44981</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3839,7 +3844,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3882,7 +3887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3896,10 +3901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45259</v>
+        <v>45702</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3917,7 +3922,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3960,7 +3965,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3974,10 +3979,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44945</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3989,8 +3994,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4033,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4047,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46127</v>
+        <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4062,13 +4072,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4111,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45702</v>
+        <v>45161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4140,13 +4145,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44882</v>
+        <v>45608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4218,13 +4218,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4267,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4277,14 +4272,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45610</v>
+        <v>45003</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4297,7 +4292,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45356</v>
+        <v>44875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4369,8 +4364,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4423,14 +4423,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45981</v>
+        <v>45826</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45565</v>
+        <v>44939</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45817</v>
+        <v>44636</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45930</v>
+        <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46149</v>
+        <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4734,8 +4734,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>16.7</v>
+        <v>10.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4778,7 +4783,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4792,10 +4797,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45078</v>
+        <v>45219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4807,8 +4812,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4851,7 +4861,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4865,10 +4875,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46167</v>
+        <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4880,8 +4890,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4924,7 +4939,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4938,10 +4953,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46177</v>
+        <v>45259</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4974,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45701</v>
+        <v>45565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5031,13 +5046,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5080,7 +5090,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5094,10 +5104,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46189</v>
+        <v>45817</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5110,7 +5120,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5153,7 +5163,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5163,14 +5173,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45373</v>
+        <v>45981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5183,7 +5193,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44524</v>
+        <v>45107</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5256,7 +5266,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5299,7 +5309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>46149</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5329,7 +5339,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>16.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5372,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44875</v>
+        <v>45314</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5407,7 +5417,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5450,7 +5460,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5460,14 +5470,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44977</v>
+        <v>45394</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5480,7 +5490,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5523,7 +5533,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5537,10 +5547,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45219</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5552,13 +5562,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45702</v>
+        <v>46167</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,13 +5635,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46260</v>
+        <v>45701</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5708,8 +5708,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5752,7 +5757,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5766,10 +5771,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44981</v>
+        <v>44882</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5781,8 +5786,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5825,7 +5835,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5835,14 +5845,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44592</v>
+        <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5855,7 +5865,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5898,7 +5908,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5912,10 +5922,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45369</v>
+        <v>45163</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5928,7 +5938,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5971,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5985,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45161</v>
+        <v>46034</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6001,7 +6011,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6044,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6058,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45356</v>
+        <v>44923</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6074,7 +6084,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6117,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6131,10 +6141,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46268</v>
+        <v>44923</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6146,13 +6156,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6195,7 +6200,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6205,14 +6210,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45003</v>
+        <v>45106</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6224,8 +6229,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6268,7 +6278,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6282,10 +6292,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45062</v>
+        <v>46177</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6297,8 +6307,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6341,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6355,10 +6370,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45145</v>
+        <v>45259</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6370,8 +6385,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6414,7 +6434,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6428,10 +6448,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45302</v>
+        <v>46043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6444,7 +6464,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6487,7 +6507,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6501,10 +6521,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44992</v>
+        <v>45370</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6522,7 +6542,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6565,7 +6585,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6579,10 +6599,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46246</v>
+        <v>46189</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6594,13 +6614,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6643,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6657,10 +6672,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45219</v>
+        <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6672,13 +6687,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6721,7 +6731,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6731,14 +6741,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45161</v>
+        <v>44592</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6751,7 +6761,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6794,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6808,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46247</v>
+        <v>45302</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6824,7 +6834,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6867,7 +6877,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6881,10 +6891,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45235</v>
+        <v>44992</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6896,8 +6906,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6954,10 +6969,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45106</v>
+        <v>46098</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6969,13 +6984,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7018,7 +7028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7032,10 +7042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45751</v>
+        <v>45259</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7047,8 +7057,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7091,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7105,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46178</v>
+        <v>45397</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7120,13 +7135,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7169,7 +7179,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7183,10 +7193,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44845</v>
+        <v>46127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7198,8 +7208,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7242,7 +7257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7256,10 +7271,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45370</v>
+        <v>45702</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7277,7 +7292,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7320,7 +7335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7334,10 +7349,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44923</v>
+        <v>44524</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7350,7 +7365,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7393,7 +7408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7407,10 +7422,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45107</v>
+        <v>45231</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7423,7 +7438,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7466,7 +7481,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7480,10 +7495,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45219</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7495,13 +7510,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>10.2</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7544,7 +7554,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7558,10 +7568,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45219</v>
+        <v>45078</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7573,13 +7583,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7622,7 +7627,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7636,10 +7641,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46276</v>
+        <v>45356</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7652,7 +7657,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7695,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7709,10 +7714,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45163</v>
+        <v>45369</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7725,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7768,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7782,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45702</v>
+        <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7797,13 +7802,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45702</v>
+        <v>45373</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7875,13 +7875,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44746</v>
+        <v>46268</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7953,8 +7948,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44992</v>
+        <v>45702</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8085,14 +8085,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45394</v>
+        <v>44977</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45265</v>
+        <v>45544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8177,13 +8177,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8226,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8240,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45511</v>
+        <v>45029</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8256,7 +8251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8299,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8313,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44879</v>
+        <v>46247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8328,13 +8323,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8377,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8391,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45666</v>
+        <v>46246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8406,8 +8396,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45477</v>
+        <v>46276</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45478</v>
+        <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8552,8 +8547,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45756</v>
+        <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 4989-2022</t>
+          <t>A 46195-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44593</v>
+        <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -881,151 +881,151 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 4989-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 4989-2022 artfynd.xlsx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 4989-2022 karta.png", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 4989-2022 georefererad karta.tif", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 4989-2022 FSC-klagomål.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 4989-2022 FSC-klagomål mail.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 4989-2022 tillsynsbegäran.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 4989-2022 tillsynsbegäran mail.docx", "A 4989-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1275/fåglar/A 4989-2022 prioriterade fågelarter.docx", "A 4989-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 46195-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44845</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/artfynd/A 46195-2022 artfynd.xlsx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor/A 46195-2022 karta.png", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/kartor_geotiff/A 46195-2022 georefererad karta.tif", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomål/A 46195-2022 FSC-klagomål.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/klagomålsmail/A 46195-2022 FSC-klagomål mail.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsyn/A 46195-2022 tillsynsbegäran.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1275/tillsynsmail/A 46195-2022 tillsynsbegäran mail.docx", "A 46195-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 26501-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45219</v>
+        <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1701,13 +1701,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1750,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26501-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1764,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44739</v>
+        <v>45751</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1780,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1840,7 +1835,7 @@
         <v>44746</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1896,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45701</v>
+        <v>45029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1969,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1983,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45265</v>
+        <v>45701</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1998,13 +1993,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2047,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2061,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45511</v>
+        <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2077,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2120,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2134,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44879</v>
+        <v>45231</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2149,13 +2139,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2198,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2212,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45078</v>
+        <v>45565</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2228,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2271,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2285,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44845</v>
+        <v>45314</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2300,8 +2285,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2344,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45583</v>
+        <v>45302</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2374,7 +2364,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2417,7 +2407,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2431,10 +2421,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45666</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2504,10 +2494,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45751</v>
+        <v>45259</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2519,8 +2509,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45302</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45478</v>
+        <v>44923</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2734,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2782,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45751</v>
+        <v>45826</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2812,7 +2807,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2855,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45259</v>
+        <v>45733</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2884,13 +2879,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2933,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2950,7 +2940,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2963,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3006,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3016,14 +3006,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45733</v>
+        <v>44939</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3036,7 +3026,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3079,7 +3069,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3093,10 +3083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45756</v>
+        <v>45259</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3108,8 +3098,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3152,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45161</v>
+        <v>45259</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3181,8 +3176,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>45583</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45602</v>
+        <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45062</v>
+        <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45235</v>
+        <v>45107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44992</v>
+        <v>45259</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44868</v>
+        <v>46098</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3668,7 +3668,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45610</v>
+        <v>45602</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>44945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44981</v>
+        <v>45702</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3843,8 +3843,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3887,7 +3892,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45702</v>
+        <v>44882</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3922,7 +3927,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3965,7 +3970,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3979,10 +3984,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3994,13 +3999,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45145</v>
+        <v>45356</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45161</v>
+        <v>45078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4206,7 +4206,7 @@
         <v>45608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45003</v>
+        <v>45701</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4291,8 +4291,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4335,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44875</v>
+        <v>45373</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4364,13 +4369,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45826</v>
+        <v>44524</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4486,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44939</v>
+        <v>45161</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44636</v>
+        <v>46127</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4588,8 +4588,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4632,7 +4637,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4642,14 +4647,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45478</v>
+        <v>45981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4662,7 +4667,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4705,7 +4710,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4719,10 +4724,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45219</v>
+        <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4740,7 +4745,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4783,7 +4788,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4797,10 +4802,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45219</v>
+        <v>44977</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4812,13 +4817,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4878,7 +4878,7 @@
         <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45259</v>
+        <v>45565</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4968,13 +4968,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5017,7 +5012,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5031,10 +5026,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45565</v>
+        <v>45817</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5047,7 +5042,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5090,7 +5085,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5104,10 +5099,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45817</v>
+        <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5120,7 +5115,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5163,7 +5158,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5173,14 +5168,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45981</v>
+        <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5192,8 +5187,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5236,7 +5236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45107</v>
+        <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46149</v>
+        <v>44981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>16.7</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45314</v>
+        <v>46043</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5411,13 +5411,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5460,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45394</v>
+        <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5490,7 +5485,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5533,7 +5528,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5563,7 +5558,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5606,7 +5601,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5620,10 +5615,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46167</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5636,7 +5631,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5679,7 +5674,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5693,10 +5688,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45701</v>
+        <v>45356</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5708,13 +5703,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5757,7 +5747,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5767,14 +5757,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44882</v>
+        <v>45003</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5786,13 +5776,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5835,7 +5820,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5849,10 +5834,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44746</v>
+        <v>46149</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5865,7 +5850,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>16.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5908,7 +5893,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5922,10 +5907,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45163</v>
+        <v>45062</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5938,7 +5923,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5966,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5980,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46034</v>
+        <v>45145</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6011,7 +5996,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6039,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6068,10 +6053,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44923</v>
+        <v>45302</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6084,7 +6069,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6127,7 +6112,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6141,10 +6126,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44923</v>
+        <v>44992</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6156,8 +6141,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6200,7 +6190,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6214,10 +6204,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45106</v>
+        <v>46167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6229,13 +6219,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6278,7 +6263,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6292,10 +6277,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46177</v>
+        <v>45219</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6313,7 +6298,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6341,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6370,10 +6355,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45259</v>
+        <v>46177</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6391,7 +6376,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6434,7 +6419,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6448,10 +6433,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46043</v>
+        <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6464,7 +6449,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6507,7 +6492,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6521,10 +6506,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45370</v>
+        <v>45235</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6536,13 +6521,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6602,7 +6582,7 @@
         <v>46189</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6658,7 +6638,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6672,10 +6652,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45565</v>
+        <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6685,6 +6665,11 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6731,7 +6716,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6741,14 +6726,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44592</v>
+        <v>45751</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6761,7 +6746,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6804,7 +6789,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6818,10 +6803,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45302</v>
+        <v>44845</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6834,7 +6819,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6877,7 +6862,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6891,10 +6876,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44992</v>
+        <v>45370</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6912,7 +6897,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6955,7 +6940,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6969,10 +6954,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46098</v>
+        <v>44923</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6985,7 +6970,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7028,7 +7013,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7042,10 +7027,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45259</v>
+        <v>45107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7057,13 +7042,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7086,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7100,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45397</v>
+        <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7135,8 +7115,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7179,7 +7164,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7193,10 +7178,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46127</v>
+        <v>45219</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7210,11 +7195,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7257,7 +7242,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7271,10 +7256,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45702</v>
+        <v>45163</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7286,13 +7271,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7335,7 +7315,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7349,10 +7329,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44524</v>
+        <v>46268</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7364,8 +7344,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7408,7 +7393,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7422,10 +7407,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45231</v>
+        <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7437,8 +7422,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7481,7 +7471,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7495,10 +7485,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45702</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7510,8 +7500,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7554,7 +7549,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7568,10 +7563,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45078</v>
+        <v>44746</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7584,7 +7579,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7627,7 +7622,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7641,10 +7636,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45356</v>
+        <v>44992</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7656,8 +7651,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7700,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7710,14 +7710,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45369</v>
+        <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45107</v>
+        <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7802,8 +7802,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7846,7 +7851,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45373</v>
+        <v>45511</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7876,7 +7881,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7924,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46268</v>
+        <v>44879</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7954,7 +7959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7997,7 +8002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45702</v>
+        <v>45666</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8026,13 +8031,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44977</v>
+        <v>45477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45544</v>
+        <v>45478</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45029</v>
+        <v>45756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,8 +8323,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8372,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,13 +8401,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46276</v>
+        <v>46178</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8474,8 +8474,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46178</v>
+        <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8547,13 +8552,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8613,7 +8613,7 @@
         <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45751</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44746</v>
+        <v>44845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45029</v>
+        <v>45702</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1920,8 +1920,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1969,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1983,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45701</v>
+        <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1999,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2042,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45078</v>
+        <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2072,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2115,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45231</v>
+        <v>45259</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2139,8 +2144,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2193,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45565</v>
+        <v>45231</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2223,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2266,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2280,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45314</v>
+        <v>45302</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2285,13 +2295,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2339,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45302</v>
+        <v>45733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2364,7 +2369,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2407,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2421,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2437,7 +2442,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2485,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45259</v>
+        <v>45161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2509,13 +2514,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>45078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44923</v>
+        <v>45356</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45544</v>
+        <v>45356</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45826</v>
+        <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45733</v>
+        <v>45107</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45733</v>
+        <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3006,14 +3006,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44939</v>
+        <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,8 +3025,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3069,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45259</v>
+        <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3096,11 +3101,6 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -3147,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45259</v>
+        <v>45544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3176,13 +3176,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3225,7 +3220,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3239,10 +3234,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45583</v>
+        <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3298,7 +3293,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3312,10 +3307,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44868</v>
+        <v>45029</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3328,7 +3323,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3371,7 +3366,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3385,10 +3380,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45478</v>
+        <v>45235</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45107</v>
+        <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3474,7 +3469,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3517,7 +3512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3531,10 +3526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45259</v>
+        <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3546,13 +3541,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3595,7 +3585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3609,10 +3599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46098</v>
+        <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3624,8 +3614,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3668,7 +3663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3682,10 +3677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45602</v>
+        <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3698,7 +3693,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3741,7 +3736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44945</v>
+        <v>45602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3771,7 +3766,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3814,7 +3809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3828,10 +3823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45702</v>
+        <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3843,13 +3838,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3892,7 +3882,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3906,10 +3896,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44882</v>
+        <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3921,13 +3911,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3970,7 +3955,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3984,10 +3969,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3999,8 +3984,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4043,7 +4033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4057,10 +4047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45356</v>
+        <v>45511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4073,7 +4063,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4116,7 +4106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4130,10 +4120,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45078</v>
+        <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4145,8 +4135,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4189,7 +4184,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4203,10 +4198,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45608</v>
+        <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4218,8 +4213,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45701</v>
+        <v>44879</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45373</v>
+        <v>44875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4369,8 +4369,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4413,7 +4418,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44524</v>
+        <v>45145</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4443,7 +4448,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4486,7 +4491,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4503,7 +4508,7 @@
         <v>45161</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4559,7 +4564,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4569,14 +4574,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46127</v>
+        <v>45003</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4588,13 +4593,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45981</v>
+        <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4739,13 +4739,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4788,7 +4783,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44977</v>
+        <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4818,7 +4813,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4861,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4875,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45219</v>
+        <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4890,13 +4885,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4939,7 +4929,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4953,10 +4943,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45565</v>
+        <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4969,7 +4959,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5012,7 +5002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5026,10 +5016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45817</v>
+        <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5042,7 +5032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5085,7 +5075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5099,10 +5089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45930</v>
+        <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5115,7 +5105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5158,7 +5148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5172,10 +5162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45702</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5193,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5250,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46034</v>
+        <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5265,8 +5255,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5309,7 +5304,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5323,10 +5318,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44981</v>
+        <v>45259</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5338,8 +5333,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46043</v>
+        <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5411,8 +5411,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5455,7 +5460,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5465,14 +5470,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44592</v>
+        <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5485,7 +5490,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5528,7 +5533,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5542,10 +5547,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45369</v>
+        <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5558,7 +5563,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5601,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5615,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45161</v>
+        <v>45314</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5630,8 +5635,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5674,7 +5684,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5684,14 +5694,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45356</v>
+        <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5704,7 +5714,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5747,7 +5757,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5757,14 +5767,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45003</v>
+        <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5777,7 +5787,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5820,7 +5830,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5834,10 +5844,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46149</v>
+        <v>45701</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5849,8 +5859,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>16.7</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5893,7 +5908,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5907,10 +5922,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45062</v>
+        <v>45826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5923,7 +5938,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5966,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5980,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45145</v>
+        <v>44882</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5995,8 +6010,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6039,7 +6059,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6053,10 +6073,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45302</v>
+        <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6069,7 +6089,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6112,7 +6132,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6126,10 +6146,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44992</v>
+        <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6141,13 +6161,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6190,7 +6205,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6204,10 +6219,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46167</v>
+        <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6219,8 +6234,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6263,7 +6283,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6277,10 +6297,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45219</v>
+        <v>44923</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6292,13 +6312,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6341,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6355,10 +6370,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46177</v>
+        <v>44923</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6370,13 +6385,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6419,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6433,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45161</v>
+        <v>45106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6448,8 +6458,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6492,7 +6507,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6506,10 +6521,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45235</v>
+        <v>45259</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6521,8 +6536,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6565,7 +6585,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6579,10 +6599,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46189</v>
+        <v>44746</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6595,7 +6615,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6638,7 +6658,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6648,14 +6668,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45106</v>
+        <v>45981</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6667,13 +6687,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6716,7 +6731,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6730,10 +6745,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45751</v>
+        <v>46098</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6746,7 +6761,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6789,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6803,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44845</v>
+        <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6816,6 +6831,11 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -6862,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6876,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45370</v>
+        <v>45078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6891,13 +6911,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6940,7 +6955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6954,10 +6969,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44923</v>
+        <v>45583</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6970,7 +6985,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7013,7 +7028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7027,10 +7042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45107</v>
+        <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7042,8 +7057,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7086,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7100,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45219</v>
+        <v>45565</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,13 +7135,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7164,7 +7179,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7174,14 +7189,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45219</v>
+        <v>44592</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7193,13 +7208,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7242,7 +7252,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7256,10 +7266,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45163</v>
+        <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7272,7 +7282,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7315,7 +7325,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7329,10 +7339,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46268</v>
+        <v>44992</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7350,7 +7360,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7393,7 +7403,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7407,10 +7417,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45702</v>
+        <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7422,13 +7432,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7471,7 +7476,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7485,10 +7490,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45702</v>
+        <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7500,13 +7505,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44746</v>
+        <v>45565</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7622,7 +7622,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44992</v>
+        <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7651,13 +7651,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7700,7 +7695,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7710,14 +7705,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45394</v>
+        <v>45259</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7729,8 +7724,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45265</v>
+        <v>46043</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7802,13 +7802,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45511</v>
+        <v>45397</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7881,7 +7876,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44879</v>
+        <v>46149</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7953,13 +7948,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8002,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8016,10 +8006,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45666</v>
+        <v>46167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8032,7 +8022,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8075,7 +8065,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8089,10 +8079,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45477</v>
+        <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8104,8 +8094,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45478</v>
+        <v>46189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45756</v>
+        <v>46268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8250,8 +8245,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,13 +8323,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8372,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8401,8 +8396,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46178</v>
+        <v>46276</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8474,13 +8474,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46276</v>
+        <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8552,8 +8547,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8613,7 +8613,7 @@
         <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45751</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45702</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45259</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45231</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45302</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45356</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45356</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45107</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45029</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45235</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44879</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45145</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45161</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45003</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45666</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45259</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45314</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45701</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>44882</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44923</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44923</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45259</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44746</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45981</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46098</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45583</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45565</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44592</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44992</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45565</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45259</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>46043</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45397</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>46149</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>46167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>46189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>46268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>46246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46276</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45751</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45702</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45751</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45259</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45231</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45302</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45356</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45356</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45107</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45544</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45062</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45029</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45235</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44868</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44992</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45511</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45702</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44879</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45145</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45161</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45003</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>45666</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45259</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45314</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45701</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>44882</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44746</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44923</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44923</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45259</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44746</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45981</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46098</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45583</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45565</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44592</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44992</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45565</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45259</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>46043</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45397</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>46149</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>46167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>46189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>46268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46247</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>46246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46276</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45751</v>
+        <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44845</v>
+        <v>45751</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45702</v>
+        <v>45602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1920,13 +1920,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1969,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1983,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44524</v>
+        <v>44746</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1999,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2042,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45751</v>
+        <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2072,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2115,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45259</v>
+        <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2144,13 +2139,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2193,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2207,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45231</v>
+        <v>46177</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2222,8 +2212,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2266,7 +2261,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45302</v>
+        <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2296,7 +2291,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2339,7 +2334,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45733</v>
+        <v>45702</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2368,8 +2363,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45733</v>
+        <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2441,8 +2441,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2485,7 +2490,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45161</v>
+        <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2515,7 +2520,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2575,7 +2580,7 @@
         <v>45078</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2631,7 +2636,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45356</v>
+        <v>44746</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2661,7 +2666,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2704,7 +2709,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45356</v>
+        <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2733,8 +2738,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2777,7 +2787,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2787,14 +2797,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45369</v>
+        <v>45394</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2807,7 +2817,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2850,7 +2860,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2864,10 +2874,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45107</v>
+        <v>45265</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2879,8 +2889,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2923,7 +2938,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2937,10 +2952,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45373</v>
+        <v>45511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2953,7 +2968,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2996,7 +3011,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3010,10 +3025,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45702</v>
+        <v>45231</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3025,13 +3040,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3074,7 +3084,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3088,10 +3098,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44977</v>
+        <v>44879</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3103,8 +3113,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3147,7 +3162,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3161,10 +3176,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45544</v>
+        <v>45666</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3177,7 +3192,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3220,7 +3235,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3234,10 +3249,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45062</v>
+        <v>45565</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3250,7 +3265,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3293,7 +3308,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3303,14 +3318,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45029</v>
+        <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3323,7 +3338,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3366,7 +3381,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3380,10 +3395,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45235</v>
+        <v>45477</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3396,7 +3411,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3439,7 +3454,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3453,10 +3468,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44868</v>
+        <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3469,7 +3484,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3512,7 +3527,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3526,10 +3541,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45701</v>
+        <v>45756</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3542,7 +3557,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3585,7 +3600,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3599,10 +3614,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44992</v>
+        <v>46268</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3620,7 +3635,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3663,7 +3678,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3677,10 +3692,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45610</v>
+        <v>45314</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3692,8 +3707,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3736,7 +3756,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3750,10 +3770,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45602</v>
+        <v>46034</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3766,7 +3786,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3809,7 +3829,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3823,10 +3843,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44945</v>
+        <v>46043</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3839,7 +3859,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3882,7 +3902,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3896,10 +3916,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44981</v>
+        <v>45826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3912,7 +3932,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3955,7 +3975,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3969,10 +3989,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45265</v>
+        <v>46246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3990,7 +4010,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4033,7 +4053,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4047,10 +4067,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45511</v>
+        <v>46247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4063,7 +4083,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4106,7 +4126,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4120,10 +4140,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45702</v>
+        <v>45302</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4135,13 +4155,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,7 +4199,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4198,10 +4213,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45702</v>
+        <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4219,7 +4234,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4262,7 +4277,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4276,10 +4291,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44879</v>
+        <v>46098</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4291,13 +4306,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4340,7 +4350,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4354,10 +4364,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44875</v>
+        <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4369,13 +4379,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4418,7 +4423,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4432,10 +4437,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45145</v>
+        <v>46276</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4448,7 +4453,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4491,7 +4496,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4505,10 +4510,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45161</v>
+        <v>45259</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4520,8 +4525,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4564,7 +4574,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4574,14 +4584,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45003</v>
+        <v>46260</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4594,7 +4604,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4637,7 +4647,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4647,14 +4657,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44939</v>
+        <v>46127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4666,8 +4676,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4710,7 +4725,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4724,10 +4739,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45666</v>
+        <v>44636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4740,7 +4755,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4783,7 +4798,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4797,10 +4812,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44636</v>
+        <v>44923</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4813,7 +4828,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4856,7 +4871,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4870,10 +4885,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45478</v>
+        <v>45565</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4886,7 +4901,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4929,7 +4944,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4943,10 +4958,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45477</v>
+        <v>45544</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4959,7 +4974,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5002,7 +5017,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5016,10 +5031,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45478</v>
+        <v>45817</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5032,7 +5047,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5075,7 +5090,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5089,10 +5104,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45756</v>
+        <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5105,7 +5120,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5148,7 +5163,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5162,10 +5177,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>45733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5177,13 +5192,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45219</v>
+        <v>45733</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5255,13 +5265,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5304,7 +5309,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5314,14 +5319,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45259</v>
+        <v>44939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5333,13 +5338,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45219</v>
+        <v>45259</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5460,7 +5460,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45608</v>
+        <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5489,8 +5489,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5533,7 +5538,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5547,10 +5552,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45107</v>
+        <v>45583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5563,7 +5568,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5606,7 +5611,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5620,10 +5625,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45314</v>
+        <v>44868</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5635,13 +5640,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5694,14 +5694,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45394</v>
+        <v>46149</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>16.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45161</v>
+        <v>45478</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45701</v>
+        <v>45107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5859,13 +5859,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5908,7 +5903,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5922,10 +5917,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45826</v>
+        <v>45259</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5937,8 +5932,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44882</v>
+        <v>44945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6010,13 +6010,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6059,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6073,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44746</v>
+        <v>46167</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6089,7 +6084,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6132,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6146,10 +6141,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45163</v>
+        <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,8 +6156,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6205,7 +6205,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45219</v>
+        <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6283,7 +6283,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44923</v>
+        <v>45610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6356,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44923</v>
+        <v>45356</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45106</v>
+        <v>45078</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,13 +6458,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6507,7 +6502,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6521,10 +6516,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45259</v>
+        <v>45701</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6542,7 +6537,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6585,7 +6580,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44746</v>
+        <v>45373</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6615,7 +6610,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6668,14 +6663,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45981</v>
+        <v>44524</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46098</v>
+        <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45370</v>
+        <v>44875</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6839,7 +6834,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6882,7 +6877,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6896,10 +6891,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45078</v>
+        <v>44977</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6955,7 +6950,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6969,10 +6964,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45583</v>
+        <v>45219</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6984,8 +6979,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7028,7 +7028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46127</v>
+        <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7059,11 +7059,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45565</v>
+        <v>44981</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7196,7 +7196,7 @@
         <v>44592</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45302</v>
+        <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7325,7 +7325,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44992</v>
+        <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7354,13 +7354,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7403,7 +7398,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7417,10 +7412,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>45356</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7433,7 +7428,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7476,7 +7471,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7486,14 +7481,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46034</v>
+        <v>45003</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7506,7 +7501,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7549,7 +7544,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7563,10 +7558,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45565</v>
+        <v>45062</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7579,7 +7574,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7622,7 +7617,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7636,10 +7631,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45817</v>
+        <v>45145</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7652,7 +7647,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7695,7 +7690,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7709,10 +7704,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45259</v>
+        <v>45302</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7724,13 +7719,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7773,7 +7763,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7787,10 +7777,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46043</v>
+        <v>44992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7802,8 +7792,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7846,7 +7841,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7860,10 +7855,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45397</v>
+        <v>45219</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7875,8 +7870,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46149</v>
+        <v>45161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>16.7</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46167</v>
+        <v>45235</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8065,7 +8065,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46177</v>
+        <v>45106</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46189</v>
+        <v>45751</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8216,7 +8216,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46268</v>
+        <v>44845</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8245,13 +8245,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46247</v>
+        <v>45370</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8323,8 +8318,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>9.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46246</v>
+        <v>44923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,13 +8396,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46276</v>
+        <v>45107</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8475,7 +8470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8518,7 +8513,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8532,10 +8527,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46178</v>
+        <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8548,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8591,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8605,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46260</v>
+        <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8625,8 +8620,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8686,7 +8686,7 @@
         <v>44637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44830</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45348</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45607</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45393</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45709</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46030</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>46043</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46044</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46213</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE141"/>
+  <dimension ref="A1:AE142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38936-2023</t>
+          <t>A 46200-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45163</v>
+        <v>44845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 16337-2025</t>
+          <t>A 1166-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45751</v>
+        <v>45302</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 28736-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45602</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28244-2022</t>
+          <t>A 28370-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44746</v>
+        <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16395-2023</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45029</v>
+        <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6948-2025</t>
+          <t>A 1538-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45701</v>
+        <v>46034</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25487-2026</t>
+          <t>A 54647-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46177</v>
+        <v>45235</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,13 +2212,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2261,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27465-2026</t>
+          <t>A 51207-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46189</v>
+        <v>44868</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2291,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2334,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7508-2025</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2348,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45702</v>
+        <v>45602</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2363,13 +2358,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2412,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7510-2025</t>
+          <t>A 53586-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2426,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45702</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2447,7 +2437,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2490,7 +2480,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 2015-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2500,14 +2490,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45608</v>
+        <v>44939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2520,7 +2510,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2563,7 +2553,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 23786-2023</t>
+          <t>A 30063-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2577,10 +2567,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45078</v>
+        <v>45826</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2593,7 +2583,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2636,7 +2626,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28247-2022</t>
+          <t>A 12182-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2650,10 +2640,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44746</v>
+        <v>44636</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2666,7 +2656,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2709,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11701-2023</t>
+          <t>A 52315-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44992</v>
+        <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2738,13 +2728,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2787,7 +2772,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14473-2024</t>
+          <t>A 3661-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2797,14 +2782,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45394</v>
+        <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2817,7 +2802,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2860,7 +2845,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61859-2023</t>
+          <t>A 60501-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2874,10 +2859,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45265</v>
+        <v>45259</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2895,7 +2880,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2938,7 +2923,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32201-2024</t>
+          <t>A 57771-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2948,14 +2933,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45511</v>
+        <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2968,7 +2953,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3011,7 +2996,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53875-2023</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3025,10 +3010,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45231</v>
+        <v>45314</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3040,8 +3025,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3084,7 +3074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54095-2022</t>
+          <t>A 38329-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3098,10 +3088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44879</v>
+        <v>45161</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3113,13 +3103,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3162,7 +3147,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 982-2025</t>
+          <t>A 7043-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3176,10 +3161,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45666</v>
+        <v>45701</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3191,8 +3176,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3235,7 +3225,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42454-2024</t>
+          <t>A 52617-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3249,10 +3239,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45565</v>
+        <v>45219</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3264,8 +3254,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3308,7 +3303,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57771-2025</t>
+          <t>A 13818-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3318,14 +3313,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45981</v>
+        <v>46098</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3338,7 +3333,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3381,7 +3376,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3395,10 +3390,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45477</v>
+        <v>44746</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3411,7 +3406,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3454,7 +3449,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 23785-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45478</v>
+        <v>45078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3484,7 +3479,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3527,7 +3522,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 18947-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3541,10 +3536,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45756</v>
+        <v>46127</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3556,8 +3551,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36225-2026</t>
+          <t>A 46737-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46268</v>
+        <v>45583</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3629,13 +3629,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3678,7 +3673,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2684-2024</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3692,10 +3687,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45314</v>
+        <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3707,13 +3702,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3756,7 +3746,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 16331-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3770,10 +3760,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46034</v>
+        <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3786,7 +3776,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3829,7 +3819,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3661-2026</t>
+          <t>A 60498-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3843,10 +3833,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46043</v>
+        <v>45259</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3858,8 +3848,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3902,7 +3897,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30063-2025</t>
+          <t>A 12911-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45826</v>
+        <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3932,7 +3927,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3975,7 +3970,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33251-2026</t>
+          <t>A 12912-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3989,10 +3984,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46246</v>
+        <v>45733</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4004,13 +3999,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4053,7 +4043,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33406-2026</t>
+          <t>A 47289-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4067,10 +4057,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46247</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4083,7 +4073,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4126,7 +4116,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4140,10 +4130,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45302</v>
+        <v>45161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4156,7 +4146,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4199,7 +4189,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25867-2026</t>
+          <t>A 8704-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4213,10 +4203,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46178</v>
+        <v>45356</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4228,13 +4218,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4277,7 +4262,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13818-2026</t>
+          <t>A 21208-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4291,10 +4276,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46098</v>
+        <v>45062</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4307,7 +4292,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4350,7 +4335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14632-2024</t>
+          <t>A 42435-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4364,10 +4349,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45397</v>
+        <v>45565</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4380,7 +4365,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4423,7 +4408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37598-2026</t>
+          <t>A 28097-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4437,10 +4422,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46276</v>
+        <v>45817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4453,7 +4438,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4496,7 +4481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60504-2023</t>
+          <t>A 11701-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4510,10 +4495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45259</v>
+        <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4531,7 +4516,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4574,7 +4559,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35193-2026</t>
+          <t>A 52740-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4588,10 +4573,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46260</v>
+        <v>45610</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4604,7 +4589,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4647,7 +4632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18947-2026</t>
+          <t>A 2950-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4661,10 +4646,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46127</v>
+        <v>44945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4676,13 +4661,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4725,7 +4705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 9368-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4739,10 +4719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44636</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4755,7 +4735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4798,7 +4778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62293-2022</t>
+          <t>A 7508-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4812,10 +4792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44923</v>
+        <v>45702</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4827,8 +4807,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4871,7 +4856,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42435-2024</t>
+          <t>A 7510-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4885,10 +4870,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45565</v>
+        <v>45702</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4900,8 +4885,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4944,7 +4934,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37890-2024</t>
+          <t>A 35194-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4958,10 +4948,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45544</v>
+        <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4974,7 +4964,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5017,7 +5007,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28097-2025</t>
+          <t>A 38328-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5031,10 +5021,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45817</v>
+        <v>45161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5047,7 +5037,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5090,7 +5080,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47289-2025</t>
+          <t>A 13267-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5100,14 +5090,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45930</v>
+        <v>45003</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5120,7 +5110,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5163,7 +5153,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12911-2025</t>
+          <t>A 21733-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5177,10 +5167,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45733</v>
+        <v>46149</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5193,7 +5183,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>16.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12912-2025</t>
+          <t>A 28751-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5250,10 +5240,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45733</v>
+        <v>45478</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5266,7 +5256,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 52575-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5319,14 +5309,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44939</v>
+        <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5338,8 +5328,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5382,7 +5377,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60501-2023</t>
+          <t>A 52583-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45259</v>
+        <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5417,7 +5412,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5460,7 +5455,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60506-2023</t>
+          <t>A 52615-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45259</v>
+        <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5495,7 +5490,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5538,7 +5533,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46737-2024</t>
+          <t>A 23874-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5552,10 +5547,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45583</v>
+        <v>46167</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5568,7 +5563,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5611,7 +5606,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 29867-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5625,10 +5620,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44868</v>
+        <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5641,7 +5636,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5684,7 +5679,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21733-2026</t>
+          <t>A 14473-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5694,14 +5689,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46149</v>
+        <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5714,7 +5709,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>16.7</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5757,7 +5752,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28751-2024</t>
+          <t>A 25487-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5771,10 +5766,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45478</v>
+        <v>46177</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5784,6 +5779,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -5830,7 +5830,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29867-2023</t>
+          <t>A 55410-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45107</v>
+        <v>44882</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5859,8 +5859,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5903,7 +5908,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60498-2023</t>
+          <t>A 27465-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5917,10 +5922,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45259</v>
+        <v>46189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5932,13 +5937,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2950-2023</t>
+          <t>A 28247-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44945</v>
+        <v>44746</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6054,7 +6054,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23874-2026</t>
+          <t>A 38936-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46167</v>
+        <v>45163</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7492-2025</t>
+          <t>A 62293-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45702</v>
+        <v>44923</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6156,13 +6156,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6205,7 +6200,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55410-2022</t>
+          <t>A 62296-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6219,10 +6214,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44882</v>
+        <v>44923</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6234,13 +6229,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6283,7 +6273,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52740-2024</t>
+          <t>A 31802-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6297,10 +6287,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45610</v>
+        <v>45106</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6312,8 +6302,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6356,7 +6351,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8704-2024</t>
+          <t>A 60504-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6370,10 +6365,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45356</v>
+        <v>45259</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6385,8 +6380,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23785-2023</t>
+          <t>A 10941-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45078</v>
+        <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,8 +6458,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6502,7 +6507,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7043-2025</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6516,10 +6521,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45701</v>
+        <v>45565</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6531,13 +6536,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11720-2024</t>
+          <t>A 4688-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6590,14 +6590,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45373</v>
+        <v>44592</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 67669-2021</t>
+          <t>A 1164-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44524</v>
+        <v>45302</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6726,7 +6726,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38324-2023</t>
+          <t>A 11669-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45161</v>
+        <v>44992</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6755,8 +6755,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 36225-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44875</v>
+        <v>46268</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6834,7 +6839,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6877,7 +6882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8565-2023</t>
+          <t>A 60506-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6891,10 +6896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44977</v>
+        <v>45259</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6906,8 +6911,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6950,7 +6960,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52615-2023</t>
+          <t>A 14632-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6964,10 +6974,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45219</v>
+        <v>45397</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6979,13 +6989,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7028,7 +7033,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7509-2025</t>
+          <t>A 7492-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7045,7 +7050,7 @@
         <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7063,7 +7068,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7106,7 +7111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9368-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7120,10 +7125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44981</v>
+        <v>44524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7136,7 +7141,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7179,7 +7184,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4688-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7189,14 +7194,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44592</v>
+        <v>45231</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7209,7 +7214,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7252,7 +7257,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10742-2024</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7266,10 +7271,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45369</v>
+        <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7282,7 +7287,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7325,7 +7330,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38329-2023</t>
+          <t>A 8741-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7339,10 +7344,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45161</v>
+        <v>45356</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7355,7 +7360,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7398,7 +7403,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8741-2024</t>
+          <t>A 10742-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7412,10 +7417,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45356</v>
+        <v>45369</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7428,7 +7433,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7471,7 +7476,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13267-2023</t>
+          <t>A 29874-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7481,14 +7486,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45003</v>
+        <v>45107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7501,7 +7506,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7544,7 +7549,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21208-2023</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7558,10 +7563,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45062</v>
+        <v>45373</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7574,7 +7579,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7617,7 +7622,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35194-2023</t>
+          <t>A 7509-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7631,10 +7636,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45145</v>
+        <v>45702</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7644,6 +7649,11 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -7690,7 +7700,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1164-2024</t>
+          <t>A 33406-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7704,10 +7714,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45302</v>
+        <v>46247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7720,7 +7730,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7763,7 +7773,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11669-2023</t>
+          <t>A 8565-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7777,10 +7787,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44992</v>
+        <v>44977</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7792,13 +7802,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7841,7 +7846,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52617-2023</t>
+          <t>A 37890-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7855,10 +7860,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45219</v>
+        <v>45544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7870,13 +7875,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38328-2023</t>
+          <t>A 33251-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45161</v>
+        <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7948,8 +7948,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7992,7 +7997,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8006,10 +8011,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45235</v>
+        <v>45029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8022,7 +8027,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8065,7 +8070,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 31802-2023</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8079,10 +8084,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45106</v>
+        <v>45701</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8094,13 +8099,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8143,7 +8143,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16331-2025</t>
+          <t>A 61859-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45751</v>
+        <v>45265</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8172,8 +8172,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 32201-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44845</v>
+        <v>45511</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8246,7 +8251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10941-2024</t>
+          <t>A 37598-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45370</v>
+        <v>46276</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8318,13 +8323,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62296-2022</t>
+          <t>A 54095-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44923</v>
+        <v>44879</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8396,8 +8396,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29874-2023</t>
+          <t>A 982-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45107</v>
+        <v>45666</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8470,7 +8475,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52575-2023</t>
+          <t>A 25867-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45219</v>
+        <v>46178</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8548,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>10.2</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52583-2023</t>
+          <t>A 35193-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8605,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45219</v>
+        <v>46260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8620,13 +8625,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,24 +8669,24 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 1482-2022</t>
+          <t>A 42534-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44637</v>
+        <v>46308</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 1708-2024</t>
+          <t>S 1482-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8752,14 +8752,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45434</v>
+        <v>44637</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8771,13 +8771,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8820,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 7204-2022</t>
+          <t>S 1708-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8834,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44918</v>
+        <v>45434</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8849,8 +8844,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 5383-2022</t>
+          <t>S 7204-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44830</v>
+        <v>44918</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>44.5</v>
+        <v>10.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 10184-2021</t>
+          <t>S 5383-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44543</v>
+        <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>17.5</v>
+        <v>44.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9039,7 +9039,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 824-2023</t>
+          <t>S 10184-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9053,10 +9053,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44988</v>
+        <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9.4</v>
+        <v>17.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9112,7 +9112,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 3915-2024</t>
+          <t>S 824-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9122,14 +9122,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45565</v>
+        <v>44988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 524-2024</t>
+          <t>S 3915-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9195,14 +9195,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45348</v>
+        <v>45565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9258,7 +9258,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 5974-2022</t>
+          <t>S 524-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44858</v>
+        <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>15.8</v>
+        <v>7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9331,7 +9331,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 4732-2024</t>
+          <t>S 5974-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45608</v>
+        <v>44858</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>15.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 1704-2024</t>
+          <t>S 4732-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45434</v>
+        <v>45608</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9433,13 +9433,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9482,7 +9477,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 823-2023</t>
+          <t>S 1704-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9496,10 +9491,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44988</v>
+        <v>45434</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9511,8 +9506,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 4252-2024</t>
+          <t>S 823-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45582</v>
+        <v>44988</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>13.8</v>
+        <v>7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 111-2023</t>
+          <t>S 4252-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44936</v>
+        <v>45582</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>40.1</v>
+        <v>13.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9701,7 +9701,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 4721-2024</t>
+          <t>S 111-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45607</v>
+        <v>44936</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>40.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9774,7 +9774,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S 109-2023</t>
+          <t>S 4721-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44936</v>
+        <v>45607</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>55.2</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9847,7 +9847,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S 1123-2024</t>
+          <t>S 109-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45393</v>
+        <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13.1</v>
+        <v>55.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9920,7 +9920,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 938-2023</t>
+          <t>S 1123-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45002</v>
+        <v>45393</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 4731-2024</t>
+          <t>S 938-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45608</v>
+        <v>45002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10066,7 +10066,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 557-2025</t>
+          <t>S 4731-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45709</v>
+        <v>45608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>31.1</v>
+        <v>11.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10139,7 +10139,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S 2486-2025</t>
+          <t>S 557-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45901</v>
+        <v>45709</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>15.1</v>
+        <v>31.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10212,7 +10212,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 46-2026</t>
+          <t>S 2486-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46030</v>
+        <v>45901</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.3</v>
+        <v>15.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 155-2026</t>
+          <t>S 46-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46043</v>
+        <v>46030</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10314,13 +10314,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10363,7 +10358,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S 172-2026</t>
+          <t>S 155-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10377,10 +10372,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10398,7 +10393,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>21.6</v>
+        <v>20</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10441,7 +10436,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S 164-2026</t>
+          <t>S 172-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10458,7 +10453,7 @@
         <v>46044</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10476,7 +10471,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10519,7 +10514,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S 168-2026</t>
+          <t>S 164-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10536,7 +10531,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10554,7 +10549,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.4</v>
+        <v>19.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10597,7 +10592,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 169-2026</t>
+          <t>S 168-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10614,7 +10609,7 @@
         <v>46044</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10632,7 +10627,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10675,7 +10670,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 306-2026</t>
+          <t>S 169-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10689,10 +10684,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10704,8 +10699,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>27.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 1178-2026</t>
+          <t>S 306-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46136</v>
+        <v>46058</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.1</v>
+        <v>27.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 2012-2026</t>
+          <t>S 1178-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46210</v>
+        <v>46136</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10850,13 +10850,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>11.1</v>
+        <v>8.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10899,7 +10894,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 2013-2026</t>
+          <t>S 2012-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10916,7 +10911,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10934,7 +10929,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>17.7</v>
+        <v>11.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10977,7 +10972,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S 2011-2026</t>
+          <t>S 2013-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10994,7 +10989,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11012,7 +11007,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>28.1</v>
+        <v>17.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11055,7 +11050,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S 2015-2026</t>
+          <t>S 2011-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11072,7 +11067,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11090,7 +11085,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11133,7 +11128,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S 2017-2026</t>
+          <t>S 2015-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11150,7 +11145,7 @@
         <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11168,123 +11163,201 @@
         </is>
       </c>
       <c r="I140" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>S 2017-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>S 2047-2026</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D141" s="1" t="n">
+      <c r="D142" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="E141" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>PERSTORP</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
+      <c r="E142" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PERSTORP</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I141" t="n">
+      <c r="I142" t="n">
         <v>18.5</v>
       </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" s="2" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PERSTORP.xlsx
+++ b/Översikt PERSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>45391</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45873</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44845</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>46020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45901</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44487</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44739</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46200-2022</t>
+          <t>A 17321-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44845</v>
+        <v>45756</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1166-2024</t>
+          <t>A 11720-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45302</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1891,7 +1891,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28736-2024</t>
+          <t>A 16337-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>45751</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28370-2024</t>
+          <t>A 28244-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45477</v>
+        <v>44746</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17321-2025</t>
+          <t>A 16395-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45756</v>
+        <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2110,7 +2110,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1538-2026</t>
+          <t>A 6948-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46034</v>
+        <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54647-2023</t>
+          <t>A 67669-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45235</v>
+        <v>44524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51207-2022</t>
+          <t>A 38324-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44868</v>
+        <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51250-2024</t>
+          <t>A 23786-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45602</v>
+        <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53586-2022</t>
+          <t>A 53875-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2431,13 +2431,8 @@
           <t>PERSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2480,7 +2475,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2015-2023</t>
+          <t>A 42454-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2490,14 +2485,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44939</v>
+        <v>45565</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2570,7 +2565,7 @@
         <v>45826</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2626,7 +2621,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12182-2022</t>
+          <t>A 2684-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2640,10 +2635,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44636</v>
+        <v>45314</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,8 +2650,13 @@
           <t>PERSTORP</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52315-2024</t>
+          <t>A 51250-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45608</v>
+        <v>45602</v>
       </c>
       <c r